--- a/script/simulation_queue.xlsx
+++ b/script/simulation_queue.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f03addda2663411/SRBL/WearableOptimizedControl/Optimizer/Moco_git/script/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="8_{985CFB64-8444-49E3-9649-B21738068EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B12FB7E-BD7F-420A-A761-074810E0541A}"/>
+  <xr:revisionPtr revIDLastSave="286" documentId="8_{985CFB64-8444-49E3-9649-B21738068EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76B3DD12-6E8F-4759-B5D5-6550E0B8B7A4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="simulation_queue" sheetId="1" r:id="rId1"/>
     <sheet name="completed_queue" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1760" uniqueCount="110">
   <si>
     <t>SF</t>
   </si>
@@ -115,17 +115,7 @@
     <t>2D_gait_AFO_pc.osim</t>
   </si>
   <si>
-    <t>modeWoC</t>
-  </si>
-  <si>
-    <t>et_a001b1_iter1</t>
-  </si>
-  <si>
     <t>modeSym</t>
-  </si>
-  <si>
-    <t>SW002-1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>ID rule : 
@@ -141,51 +131,324 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">default QP_effort </t>
+    <t>[0.4 1.0]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>modeSym'</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>default QP_smooth</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>default mocoEffort</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>default mocoFinalTime</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>default mocoTimeBound</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>default mocoDistBound</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>default gaitMode</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>modeOff</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>modeSpline</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>available optMode</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>modeOff'</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>modeSpline'</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>et</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF001-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF002-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF003-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF004-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF005-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF006-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF007-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF008-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF009-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF010-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF011-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF012-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP001-100</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>default QP_effort</t>
+  </si>
+  <si>
+    <t>[0 10]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF013-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0 5]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0.4 10]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0.4 3]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0.4 5]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF014-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF015-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF016-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF017-3</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>[0.4 0.8]</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>[0.4 1.0]</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>modeSym'</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>default QP_smooth</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>default mocoEffort</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>default mocoFinalTime</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>default mocoTimeBound</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>default mocoDistBound</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>default gaitMode</t>
+  </si>
+  <si>
+    <t>[0.2 2.0]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF018-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF019-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF020-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF021-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF022-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_40BW.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP002-300</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP003-300</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_50BW.osim</t>
+  </si>
+  <si>
+    <t>modeWoC</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>modeWoC'</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW001-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW002-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW003-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW004-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW005-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW006-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW007-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW008-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW009-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW010-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW011-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW012-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW013-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW014-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW015-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW016-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW017-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW018-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW019-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW020-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW021-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW022-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF023-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0.4 1.6]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0.4 2.4]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0.1 10]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF024-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF025-3</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -395,19 +658,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79995117038483843"/>
+        <fgColor theme="4" tint="0.79995117038484"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59996337778862885"/>
+        <fgColor theme="4" tint="0.59996337778863"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.39997558519242"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -418,19 +681,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79995117038483843"/>
+        <fgColor theme="5" tint="0.79995117038484"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59996337778862885"/>
+        <fgColor theme="5" tint="0.59996337778863"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.39997558519242"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -441,19 +704,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79995117038483843"/>
+        <fgColor theme="6" tint="0.79995117038484"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59996337778862885"/>
+        <fgColor theme="6" tint="0.59996337778863"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
+        <fgColor theme="6" tint="0.39997558519242"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -464,19 +727,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79995117038483843"/>
+        <fgColor theme="7" tint="0.79995117038484"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59996337778862885"/>
+        <fgColor theme="7" tint="0.59996337778863"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor theme="7" tint="0.39997558519242"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -487,19 +750,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79995117038483843"/>
+        <fgColor theme="8" tint="0.79995117038484"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59996337778862885"/>
+        <fgColor theme="8" tint="0.59996337778863"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
+        <fgColor theme="8" tint="0.39997558519242"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -510,24 +773,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79995117038483843"/>
+        <fgColor theme="9" tint="0.79995117038484"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59996337778862885"/>
+        <fgColor theme="9" tint="0.59996337778863"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="9" tint="0.39997558519242"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -549,7 +812,7 @@
       <right/>
       <top/>
       <bottom style="thick">
-        <color theme="4" tint="0.49995422223578601"/>
+        <color theme="4" tint="0.49995422223579"/>
       </bottom>
       <diagonal/>
     </border>
@@ -558,7 +821,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.39997558519242"/>
       </bottom>
       <diagonal/>
     </border>
@@ -642,191 +905,196 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="false" applyFont="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="강조색1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="강조색2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="강조색3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="강조색4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="강조색5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="강조색6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="경고문" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="계산" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="나쁨" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="메모" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="보통" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="설명 텍스트" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="셀 확인" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="연결된 셀" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="요약" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="입력" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="제목" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="제목 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="제목 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="제목 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="제목 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="좋음" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="true"/>
+    <cellStyle name="20% - 강조색2" xfId="23" builtinId="34" customBuiltin="true"/>
+    <cellStyle name="20% - 강조색3" xfId="27" builtinId="38" customBuiltin="true"/>
+    <cellStyle name="20% - 강조색4" xfId="31" builtinId="42" customBuiltin="true"/>
+    <cellStyle name="20% - 강조색5" xfId="35" builtinId="46" customBuiltin="true"/>
+    <cellStyle name="20% - 강조색6" xfId="39" builtinId="50" customBuiltin="true"/>
+    <cellStyle name="40% - 강조색1" xfId="20" builtinId="31" customBuiltin="true"/>
+    <cellStyle name="40% - 강조색2" xfId="24" builtinId="35" customBuiltin="true"/>
+    <cellStyle name="40% - 강조색3" xfId="28" builtinId="39" customBuiltin="true"/>
+    <cellStyle name="40% - 강조색4" xfId="32" builtinId="43" customBuiltin="true"/>
+    <cellStyle name="40% - 강조색5" xfId="36" builtinId="47" customBuiltin="true"/>
+    <cellStyle name="40% - 강조색6" xfId="40" builtinId="51" customBuiltin="true"/>
+    <cellStyle name="60% - 강조색1" xfId="21" builtinId="32" customBuiltin="true"/>
+    <cellStyle name="60% - 강조색2" xfId="25" builtinId="36" customBuiltin="true"/>
+    <cellStyle name="60% - 강조색3" xfId="29" builtinId="40" customBuiltin="true"/>
+    <cellStyle name="60% - 강조색4" xfId="33" builtinId="44" customBuiltin="true"/>
+    <cellStyle name="60% - 강조색5" xfId="37" builtinId="48" customBuiltin="true"/>
+    <cellStyle name="60% - 강조색6" xfId="41" builtinId="52" customBuiltin="true"/>
+    <cellStyle name="강조색1" xfId="18" builtinId="29" customBuiltin="true"/>
+    <cellStyle name="강조색2" xfId="22" builtinId="33" customBuiltin="true"/>
+    <cellStyle name="강조색3" xfId="26" builtinId="37" customBuiltin="true"/>
+    <cellStyle name="강조색4" xfId="30" builtinId="41" customBuiltin="true"/>
+    <cellStyle name="강조색5" xfId="34" builtinId="45" customBuiltin="true"/>
+    <cellStyle name="강조색6" xfId="38" builtinId="49" customBuiltin="true"/>
+    <cellStyle name="경고문" xfId="14" builtinId="11" customBuiltin="true"/>
+    <cellStyle name="계산" xfId="11" builtinId="22" customBuiltin="true"/>
+    <cellStyle name="나쁨" xfId="7" builtinId="27" customBuiltin="true"/>
+    <cellStyle name="메모" xfId="15" builtinId="10" customBuiltin="true"/>
+    <cellStyle name="보통" xfId="8" builtinId="28" customBuiltin="true"/>
+    <cellStyle name="설명 텍스트" xfId="16" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="셀 확인" xfId="13" builtinId="23" customBuiltin="true"/>
+    <cellStyle name="연결된 셀" xfId="12" builtinId="24" customBuiltin="true"/>
+    <cellStyle name="요약" xfId="17" builtinId="25" customBuiltin="true"/>
+    <cellStyle name="입력" xfId="9" builtinId="20" customBuiltin="true"/>
+    <cellStyle name="제목" xfId="1" builtinId="15" customBuiltin="true"/>
+    <cellStyle name="제목 1" xfId="2" builtinId="16" customBuiltin="true"/>
+    <cellStyle name="제목 2" xfId="3" builtinId="17" customBuiltin="true"/>
+    <cellStyle name="제목 3" xfId="4" builtinId="18" customBuiltin="true"/>
+    <cellStyle name="제목 4" xfId="5" builtinId="19" customBuiltin="true"/>
+    <cellStyle name="좋음" xfId="6" builtinId="26" customBuiltin="true"/>
+    <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="true"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -843,7 +1111,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -994,7 +1262,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1018,9 +1286,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1044,7 +1312,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1079,7 +1347,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1097,7 +1365,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1122,7 +1390,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1138,197 +1406,436 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U11"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U14"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.375" customWidth="1"/>
-    <col min="2" max="2" width="13.125" customWidth="1"/>
-    <col min="3" max="3" width="22.375" customWidth="1"/>
-    <col min="4" max="4" width="8.25" customWidth="1"/>
-    <col min="5" max="5" width="13.5" customWidth="1"/>
-    <col min="6" max="6" width="6.875" customWidth="1"/>
-    <col min="7" max="7" width="4.125" customWidth="1"/>
-    <col min="8" max="8" width="4" customWidth="1"/>
-    <col min="9" max="9" width="3.875" customWidth="1"/>
-    <col min="10" max="10" width="7.5" customWidth="1"/>
-    <col min="11" max="11" width="11.375" customWidth="1"/>
-    <col min="12" max="12" width="9.25" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="4.625" customWidth="1"/>
-    <col min="15" max="15" width="10.625" customWidth="1"/>
-    <col min="16" max="16" width="14.125" customWidth="1"/>
-    <col min="17" max="17" width="15.75" customWidth="1"/>
-    <col min="18" max="18" width="14.875" customWidth="1"/>
-    <col min="19" max="19" width="9.5" customWidth="1"/>
-    <col min="20" max="20" width="12.875" customWidth="1"/>
-    <col min="21" max="21" width="9.5" customWidth="1"/>
+    <col min="1" max="1" width="25.75" customWidth="true"/>
+    <col min="2" max="2" width="10.625" customWidth="true"/>
+    <col min="3" max="3" width="9.25" customWidth="true"/>
+    <col min="4" max="4" width="11.75" customWidth="true"/>
+    <col min="5" max="5" width="13.5" customWidth="true"/>
+    <col min="6" max="6" width="6.875" customWidth="true"/>
+    <col min="7" max="7" width="4.125" customWidth="true"/>
+    <col min="8" max="8" width="4" customWidth="true"/>
+    <col min="9" max="9" width="3.875" customWidth="true"/>
+    <col min="10" max="10" width="7.5" customWidth="true"/>
+    <col min="11" max="11" width="11.375" customWidth="true"/>
+    <col min="12" max="12" width="9.25" customWidth="true"/>
+    <col min="13" max="13" width="11" customWidth="true"/>
+    <col min="14" max="14" width="4.625" customWidth="true"/>
+    <col min="15" max="15" width="10.625" customWidth="true"/>
+    <col min="16" max="16" width="14.125" customWidth="true"/>
+    <col min="17" max="17" width="15.75" customWidth="true"/>
+    <col min="18" max="18" width="14.875" customWidth="true"/>
+    <col min="19" max="19" width="9.5" customWidth="true"/>
+    <col min="20" max="20" width="12.875" customWidth="true"/>
+    <col min="21" max="21" width="9.5" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="B1" s="2">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C1" s="0"/>
+      <c r="D1" s="0"/>
+      <c r="E1" s="0"/>
+      <c r="F1" s="0"/>
+      <c r="G1" s="0"/>
+      <c r="H1" s="0"/>
+      <c r="I1" s="0"/>
+      <c r="J1" s="0"/>
+      <c r="K1" s="0"/>
+      <c r="L1" s="0"/>
+      <c r="M1" s="0"/>
+      <c r="N1" s="0"/>
+      <c r="O1" s="0"/>
+      <c r="P1" s="0"/>
+      <c r="Q1" s="0"/>
+      <c r="R1" s="0"/>
+      <c r="S1" s="0"/>
+      <c r="T1" s="0"/>
+      <c r="U1" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C2" s="0"/>
+      <c r="D2" s="0"/>
+      <c r="E2" s="0"/>
+      <c r="F2" s="0"/>
+      <c r="G2" s="0"/>
+      <c r="H2" s="0"/>
+      <c r="I2" s="0"/>
+      <c r="J2" s="0"/>
+      <c r="K2" s="0"/>
+      <c r="L2" s="0"/>
+      <c r="M2" s="0"/>
+      <c r="N2" s="0"/>
+      <c r="O2" s="0"/>
+      <c r="P2" s="0"/>
+      <c r="Q2" s="0"/>
+      <c r="R2" s="0"/>
+      <c r="S2" s="0"/>
+      <c r="T2" s="0"/>
+      <c r="U2" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C3" s="0"/>
+      <c r="D3" s="0"/>
+      <c r="E3" s="0"/>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
+      <c r="I3" s="0"/>
+      <c r="J3" s="0"/>
+      <c r="K3" s="0"/>
+      <c r="L3" s="0"/>
+      <c r="M3" s="0"/>
+      <c r="N3" s="0"/>
+      <c r="O3" s="0"/>
+      <c r="P3" s="0"/>
+      <c r="Q3" s="0"/>
+      <c r="R3" s="0"/>
+      <c r="S3" s="0"/>
+      <c r="T3" s="0"/>
+      <c r="U3" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="C4" s="0"/>
+      <c r="D4" s="0"/>
+      <c r="E4" s="0"/>
+      <c r="F4" s="0"/>
+      <c r="G4" s="0"/>
+      <c r="H4" s="0"/>
+      <c r="I4" s="0"/>
+      <c r="J4" s="0"/>
+      <c r="K4" s="0"/>
+      <c r="L4" s="0"/>
+      <c r="M4" s="0"/>
+      <c r="N4" s="0"/>
+      <c r="O4" s="0"/>
+      <c r="P4" s="0"/>
+      <c r="Q4" s="0"/>
+      <c r="R4" s="0"/>
+      <c r="S4" s="0"/>
+      <c r="T4" s="0"/>
+      <c r="U4" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="0"/>
+      <c r="D5" s="0"/>
+      <c r="E5" s="0"/>
+      <c r="F5" s="0"/>
+      <c r="G5" s="0"/>
+      <c r="H5" s="0"/>
+      <c r="I5" s="0"/>
+      <c r="J5" s="0"/>
+      <c r="K5" s="0"/>
+      <c r="L5" s="0"/>
+      <c r="M5" s="0"/>
+      <c r="N5" s="0"/>
+      <c r="O5" s="0"/>
+      <c r="P5" s="0"/>
+      <c r="Q5" s="0"/>
+      <c r="R5" s="0"/>
+      <c r="S5" s="0"/>
+      <c r="T5" s="0"/>
+      <c r="U5" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="0"/>
+      <c r="D6" s="0"/>
+      <c r="E6" s="0"/>
+      <c r="F6" s="0"/>
+      <c r="G6" s="0"/>
+      <c r="H6" s="0"/>
+      <c r="I6" s="0"/>
+      <c r="J6" s="0"/>
+      <c r="K6" s="0"/>
+      <c r="L6" s="0"/>
+      <c r="M6" s="0"/>
+      <c r="N6" s="0"/>
+      <c r="O6" s="0"/>
+      <c r="P6" s="0"/>
+      <c r="Q6" s="0"/>
+      <c r="R6" s="0"/>
+      <c r="S6" s="0"/>
+      <c r="T6" s="0"/>
+      <c r="U6" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="0"/>
+      <c r="D7" s="0"/>
+      <c r="E7" s="0"/>
+      <c r="F7" s="0"/>
+      <c r="G7" s="0"/>
+      <c r="H7" s="0"/>
+      <c r="I7" s="0"/>
+      <c r="J7" s="0"/>
+      <c r="K7" s="0"/>
+      <c r="L7" s="0"/>
+      <c r="M7" s="0"/>
+      <c r="N7" s="0"/>
+      <c r="O7" s="0"/>
+      <c r="P7" s="0"/>
+      <c r="Q7" s="0"/>
+      <c r="R7" s="0"/>
+      <c r="S7" s="0"/>
+      <c r="T7" s="0"/>
+      <c r="U7" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="165" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="E8" s="0"/>
+      <c r="F8" s="0"/>
+      <c r="G8" s="0"/>
+      <c r="H8" s="0"/>
+      <c r="I8" s="0"/>
+      <c r="J8" s="0"/>
+      <c r="K8" s="0"/>
+      <c r="L8" s="0"/>
+      <c r="M8" s="0"/>
+      <c r="N8" s="0"/>
+      <c r="O8" s="0"/>
+      <c r="P8" s="0"/>
+      <c r="Q8" s="0"/>
+      <c r="R8" s="0"/>
+      <c r="S8" s="0"/>
+      <c r="T8" s="0"/>
+      <c r="U8" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" ht="165" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="0"/>
+      <c r="D9" s="0"/>
+      <c r="E9" s="0"/>
+      <c r="F9" s="0"/>
+      <c r="G9" s="0"/>
+      <c r="H9" s="0"/>
+      <c r="I9" s="0"/>
+      <c r="J9" s="0"/>
+      <c r="K9" s="0"/>
+      <c r="L9" s="0"/>
+      <c r="M9" s="0"/>
+      <c r="N9" s="0"/>
+      <c r="O9" s="0"/>
+      <c r="P9" s="0"/>
+      <c r="Q9" s="0"/>
+      <c r="R9" s="0"/>
+      <c r="S9" s="0"/>
+      <c r="T9" s="0"/>
+      <c r="U9" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="B10" s="2"/>
+      <c r="C10" s="0"/>
+      <c r="D10" s="0"/>
+      <c r="E10" s="0"/>
+      <c r="F10" s="0"/>
+      <c r="G10" s="0"/>
+      <c r="H10" s="0"/>
+      <c r="I10" s="0"/>
+      <c r="J10" s="0"/>
+      <c r="K10" s="0"/>
+      <c r="L10" s="0"/>
+      <c r="M10" s="0"/>
+      <c r="N10" s="0"/>
+      <c r="O10" s="0"/>
+      <c r="P10" s="0"/>
+      <c r="Q10" s="0"/>
+      <c r="R10" s="0"/>
+      <c r="S10" s="0"/>
+      <c r="T10" s="0"/>
+      <c r="U10" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E11" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F11" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G11" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H11" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I11" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J11" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K11" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L11" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="M10" t="s">
+      <c r="M11" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="N10" t="s">
+      <c r="N11" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="O10" t="s">
+      <c r="O11" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="P10" t="s">
+      <c r="P11" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="Q11" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="R10" t="s">
+      <c r="R11" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="S10" t="s">
+      <c r="S11" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="T10" t="s">
+      <c r="T11" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="U10" t="s">
+      <c r="U11" s="0" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="2">
-        <v>260416</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>29</v>
-      </c>
-      <c r="K11" t="s">
-        <v>30</v>
-      </c>
-      <c r="L11">
-        <v>0.01</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="S11" t="s">
-        <v>31</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.3">
+      <c r="A12" s="0"/>
+      <c r="B12" s="0"/>
+      <c r="C12" s="0"/>
+      <c r="D12" s="0"/>
+      <c r="E12" s="0"/>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
+      <c r="H12" s="0"/>
+      <c r="I12" s="0"/>
+      <c r="J12" s="0"/>
+      <c r="K12" s="0"/>
+      <c r="L12" s="0"/>
+      <c r="M12" s="0"/>
+      <c r="N12" s="0"/>
+      <c r="O12" s="0"/>
+      <c r="P12" s="0"/>
+      <c r="Q12" s="0"/>
+      <c r="R12" s="0"/>
+      <c r="S12" s="0"/>
+      <c r="T12" s="0"/>
+      <c r="U12" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.3">
+      <c r="A13" s="0"/>
+      <c r="B13" s="0"/>
+      <c r="C13" s="0"/>
+      <c r="D13" s="0"/>
+      <c r="E13" s="0"/>
+      <c r="F13" s="0"/>
+      <c r="G13" s="0"/>
+      <c r="H13" s="0"/>
+      <c r="I13" s="0"/>
+      <c r="J13" s="0"/>
+      <c r="K13" s="0"/>
+      <c r="L13" s="0"/>
+      <c r="M13" s="0"/>
+      <c r="N13" s="0"/>
+      <c r="O13" s="0"/>
+      <c r="P13" s="0"/>
+      <c r="Q13" s="0"/>
+      <c r="R13" s="0"/>
+      <c r="S13" s="0"/>
+      <c r="T13" s="0"/>
+      <c r="U13" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.3">
+      <c r="A14" s="0"/>
+      <c r="B14" s="0"/>
+      <c r="C14" s="0"/>
+      <c r="D14" s="0"/>
+      <c r="E14" s="0"/>
+      <c r="F14" s="0"/>
+      <c r="G14" s="0"/>
+      <c r="H14" s="0"/>
+      <c r="I14" s="0"/>
+      <c r="J14" s="0"/>
+      <c r="K14" s="0"/>
+      <c r="L14" s="0"/>
+      <c r="M14" s="0"/>
+      <c r="N14" s="0"/>
+      <c r="O14" s="0"/>
+      <c r="P14" s="0"/>
+      <c r="Q14" s="0"/>
+      <c r="R14" s="0"/>
+      <c r="S14" s="0"/>
+      <c r="T14" s="0"/>
+      <c r="U14" s="0"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
@@ -1338,149 +1845,2813 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFFA8AF3-BD89-432D-8740-30DBF5179C15}">
-  <dimension ref="A1:U8"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFFA8AF3-BD89-432D-8740-30DBF5179C15}">
+  <dimension ref="A1:U58"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.375" customWidth="1"/>
-    <col min="2" max="2" width="7.25" customWidth="1"/>
-    <col min="3" max="3" width="24.75" customWidth="1"/>
-    <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="13.5" customWidth="1"/>
-    <col min="6" max="6" width="6.875" customWidth="1"/>
-    <col min="7" max="7" width="4.125" customWidth="1"/>
-    <col min="8" max="8" width="4" customWidth="1"/>
-    <col min="9" max="9" width="3.875" customWidth="1"/>
-    <col min="10" max="10" width="7.5" customWidth="1"/>
-    <col min="11" max="11" width="14.25" customWidth="1"/>
-    <col min="12" max="12" width="9.25" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="4.625" customWidth="1"/>
-    <col min="15" max="15" width="10.625" customWidth="1"/>
-    <col min="16" max="16" width="14.125" customWidth="1"/>
-    <col min="17" max="17" width="15.75" customWidth="1"/>
-    <col min="18" max="18" width="14.875" customWidth="1"/>
-    <col min="19" max="19" width="9.625" customWidth="1"/>
-    <col min="20" max="20" width="12.875" customWidth="1"/>
-    <col min="21" max="21" width="9.5" customWidth="1"/>
+    <col min="1" max="1" width="10.375" customWidth="true"/>
+    <col min="2" max="2" width="7.25" customWidth="true"/>
+    <col min="3" max="3" width="24.75" customWidth="true"/>
+    <col min="4" max="4" width="4.25" customWidth="true"/>
+    <col min="5" max="5" width="13.5" customWidth="true"/>
+    <col min="6" max="6" width="6.875" customWidth="true"/>
+    <col min="7" max="7" width="4.625" customWidth="true"/>
+    <col min="10" max="10" width="7.5" customWidth="true"/>
+    <col min="11" max="11" width="11.375" customWidth="true"/>
+    <col min="12" max="12" width="9.25" customWidth="true"/>
+    <col min="13" max="13" width="11" customWidth="true"/>
+    <col min="14" max="14" width="4.625" customWidth="true"/>
+    <col min="15" max="15" width="10.625" customWidth="true"/>
+    <col min="16" max="16" width="14.125" customWidth="true"/>
+    <col min="17" max="17" width="15.75" customWidth="true"/>
+    <col min="18" max="18" width="14.875" customWidth="true"/>
+    <col min="19" max="19" width="9.625" customWidth="true"/>
+    <col min="20" max="20" width="12.875" customWidth="true"/>
+    <col min="21" max="21" width="9.5" customWidth="true"/>
+    <col min="8" max="8" width="4.625" customWidth="true"/>
+    <col min="9" max="9" width="4.625" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="0">
+        <v>25</v>
+      </c>
+      <c r="C1" s="0"/>
+      <c r="D1" s="0"/>
+      <c r="E1" s="0"/>
+      <c r="F1" s="0"/>
+      <c r="G1" s="0"/>
+      <c r="H1" s="0"/>
+      <c r="I1" s="0"/>
+      <c r="J1" s="0"/>
+      <c r="K1" s="0"/>
+      <c r="L1" s="0"/>
+      <c r="M1" s="0"/>
+      <c r="N1" s="0"/>
+      <c r="O1" s="0"/>
+      <c r="P1" s="0"/>
+      <c r="Q1" s="0"/>
+      <c r="R1" s="0"/>
+      <c r="S1" s="0"/>
+      <c r="T1" s="0"/>
+      <c r="U1" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.3">
+      <c r="A2" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0">
+        <v>22</v>
+      </c>
+      <c r="C2" s="0"/>
+      <c r="D2" s="0"/>
+      <c r="E2" s="0"/>
+      <c r="F2" s="0"/>
+      <c r="G2" s="0"/>
+      <c r="H2" s="0"/>
+      <c r="I2" s="0"/>
+      <c r="J2" s="0"/>
+      <c r="K2" s="0"/>
+      <c r="L2" s="0"/>
+      <c r="M2" s="0"/>
+      <c r="N2" s="0"/>
+      <c r="O2" s="0"/>
+      <c r="P2" s="0"/>
+      <c r="Q2" s="0"/>
+      <c r="R2" s="0"/>
+      <c r="S2" s="0"/>
+      <c r="T2" s="0"/>
+      <c r="U2" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.3">
+      <c r="A3" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0">
+        <v>3</v>
+      </c>
+      <c r="C3" s="0"/>
+      <c r="D3" s="0"/>
+      <c r="E3" s="0"/>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
+      <c r="I3" s="0"/>
+      <c r="J3" s="0"/>
+      <c r="K3" s="0"/>
+      <c r="L3" s="0"/>
+      <c r="M3" s="0"/>
+      <c r="N3" s="0"/>
+      <c r="O3" s="0"/>
+      <c r="P3" s="0"/>
+      <c r="Q3" s="0"/>
+      <c r="R3" s="0"/>
+      <c r="S3" s="0"/>
+      <c r="T3" s="0"/>
+      <c r="U3" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.3">
+      <c r="A4" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
+      <c r="C4" s="0"/>
+      <c r="D4" s="0"/>
+      <c r="E4" s="0"/>
+      <c r="F4" s="0"/>
+      <c r="G4" s="0"/>
+      <c r="H4" s="0"/>
+      <c r="I4" s="0"/>
+      <c r="J4" s="0"/>
+      <c r="K4" s="0"/>
+      <c r="L4" s="0"/>
+      <c r="M4" s="0"/>
+      <c r="N4" s="0"/>
+      <c r="O4" s="0"/>
+      <c r="P4" s="0"/>
+      <c r="Q4" s="0"/>
+      <c r="R4" s="0"/>
+      <c r="S4" s="0"/>
+      <c r="T4" s="0"/>
+      <c r="U4" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.3">
+      <c r="A5" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="C5" s="0"/>
+      <c r="D5" s="0"/>
+      <c r="E5" s="0"/>
+      <c r="F5" s="0"/>
+      <c r="G5" s="0"/>
+      <c r="H5" s="0"/>
+      <c r="I5" s="0"/>
+      <c r="J5" s="0"/>
+      <c r="K5" s="0"/>
+      <c r="L5" s="0"/>
+      <c r="M5" s="0"/>
+      <c r="N5" s="0"/>
+      <c r="O5" s="0"/>
+      <c r="P5" s="0"/>
+      <c r="Q5" s="0"/>
+      <c r="R5" s="0"/>
+      <c r="S5" s="0"/>
+      <c r="T5" s="0"/>
+      <c r="U5" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.3">
+      <c r="A6" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0">
+        <v>0</v>
+      </c>
+      <c r="C6" s="0"/>
+      <c r="D6" s="0"/>
+      <c r="E6" s="0"/>
+      <c r="F6" s="0"/>
+      <c r="G6" s="0"/>
+      <c r="H6" s="0"/>
+      <c r="I6" s="0"/>
+      <c r="J6" s="0"/>
+      <c r="K6" s="0"/>
+      <c r="L6" s="0"/>
+      <c r="M6" s="0"/>
+      <c r="N6" s="0"/>
+      <c r="O6" s="0"/>
+      <c r="P6" s="0"/>
+      <c r="Q6" s="0"/>
+      <c r="R6" s="0"/>
+      <c r="S6" s="0"/>
+      <c r="T6" s="0"/>
+      <c r="U6" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.3">
+      <c r="A7" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0"/>
+      <c r="C7" s="0"/>
+      <c r="D7" s="0"/>
+      <c r="E7" s="0"/>
+      <c r="F7" s="0"/>
+      <c r="G7" s="0"/>
+      <c r="H7" s="0"/>
+      <c r="I7" s="0"/>
+      <c r="J7" s="0"/>
+      <c r="K7" s="0"/>
+      <c r="L7" s="0"/>
+      <c r="M7" s="0"/>
+      <c r="N7" s="0"/>
+      <c r="O7" s="0"/>
+      <c r="P7" s="0"/>
+      <c r="Q7" s="0"/>
+      <c r="R7" s="0"/>
+      <c r="S7" s="0"/>
+      <c r="T7" s="0"/>
+      <c r="U7" s="0"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.3">
+      <c r="A8" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="N8" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="O8" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="P8" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q8" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="R8" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="S8" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T8" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="U8" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.3">
+      <c r="A9" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="0">
+        <v>260416</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="0">
+        <v>3</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="0"/>
+      <c r="G9" s="0"/>
+      <c r="H9" s="0"/>
+      <c r="I9" s="0"/>
+      <c r="J9" s="0"/>
+      <c r="K9" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" s="0"/>
+      <c r="M9" s="0"/>
+      <c r="N9" s="0"/>
+      <c r="O9" s="0">
+        <v>1</v>
+      </c>
+      <c r="P9" s="0">
+        <v>0.001</v>
+      </c>
+      <c r="Q9" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R9" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S9" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T9" s="0"/>
+      <c r="U9" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.3">
+      <c r="A10" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="0">
+        <v>260416</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="0">
+        <v>3</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="0"/>
+      <c r="G10" s="0"/>
+      <c r="H10" s="0"/>
+      <c r="I10" s="0"/>
+      <c r="J10" s="0"/>
+      <c r="K10" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" s="0"/>
+      <c r="M10" s="0"/>
+      <c r="N10" s="0"/>
+      <c r="O10" s="0">
+        <v>1</v>
+      </c>
+      <c r="P10" s="0">
+        <v>0.0050000000000000001</v>
+      </c>
+      <c r="Q10" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R10" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S10" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T10" s="0"/>
+      <c r="U10" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.3">
+      <c r="A11" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="0">
+        <v>260416</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="0">
+        <v>3</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0"/>
+      <c r="H11" s="0"/>
+      <c r="I11" s="0"/>
+      <c r="J11" s="0"/>
+      <c r="K11" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="L11" s="0"/>
+      <c r="M11" s="0"/>
+      <c r="N11" s="0"/>
+      <c r="O11" s="0">
+        <v>1</v>
+      </c>
+      <c r="P11" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="Q11" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R11" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S11" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T11" s="0"/>
+      <c r="U11" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.3">
+      <c r="A12" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="0">
+        <v>260416</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="0">
+        <v>3</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
+      <c r="H12" s="0"/>
+      <c r="I12" s="0"/>
+      <c r="J12" s="0"/>
+      <c r="K12" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="L12" s="0"/>
+      <c r="M12" s="0"/>
+      <c r="N12" s="0"/>
+      <c r="O12" s="0">
+        <v>1</v>
+      </c>
+      <c r="P12" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q12" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R12" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S12" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T12" s="0"/>
+      <c r="U12" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.3">
+      <c r="A13" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="0">
+        <v>260416</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="0">
+        <v>3</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="0"/>
+      <c r="G13" s="0"/>
+      <c r="H13" s="0"/>
+      <c r="I13" s="0"/>
+      <c r="J13" s="0"/>
+      <c r="K13" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="0"/>
+      <c r="M13" s="0"/>
+      <c r="N13" s="0"/>
+      <c r="O13" s="0">
+        <v>1</v>
+      </c>
+      <c r="P13" s="0">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="Q13" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R13" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S13" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T13" s="0"/>
+      <c r="U13" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.3">
+      <c r="A14" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="0">
+        <v>260416</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="0">
+        <v>3</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="0"/>
+      <c r="G14" s="0"/>
+      <c r="H14" s="0"/>
+      <c r="I14" s="0"/>
+      <c r="J14" s="0"/>
+      <c r="K14" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="L14" s="0"/>
+      <c r="M14" s="0"/>
+      <c r="N14" s="0"/>
+      <c r="O14" s="0">
+        <v>1</v>
+      </c>
+      <c r="P14" s="0">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="Q14" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R14" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S14" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T14" s="0"/>
+      <c r="U14" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.3">
+      <c r="A15" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="0">
+        <v>260416</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="0">
+        <v>3</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="0"/>
+      <c r="G15" s="0"/>
+      <c r="H15" s="0"/>
+      <c r="I15" s="0"/>
+      <c r="J15" s="0"/>
+      <c r="K15" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="L15" s="0"/>
+      <c r="M15" s="0"/>
+      <c r="N15" s="0"/>
+      <c r="O15" s="0">
+        <v>1</v>
+      </c>
+      <c r="P15" s="0">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="Q15" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R15" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S15" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T15" s="0"/>
+      <c r="U15" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.3">
+      <c r="A16" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="0">
+        <v>260416</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="0">
+        <v>3</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="0"/>
+      <c r="G16" s="0"/>
+      <c r="H16" s="0"/>
+      <c r="I16" s="0"/>
+      <c r="J16" s="0"/>
+      <c r="K16" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="L16" s="0"/>
+      <c r="M16" s="0"/>
+      <c r="N16" s="0"/>
+      <c r="O16" s="0">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="P16" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q16" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R16" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S16" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T16" s="0"/>
+      <c r="U16" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.3">
+      <c r="A17" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="0">
+        <v>260416</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="0">
+        <v>3</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="0"/>
+      <c r="G17" s="0"/>
+      <c r="H17" s="0"/>
+      <c r="I17" s="0"/>
+      <c r="J17" s="0"/>
+      <c r="K17" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L17" s="0"/>
+      <c r="M17" s="0"/>
+      <c r="N17" s="0"/>
+      <c r="O17" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="P17" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q17" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R17" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S17" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T17" s="0"/>
+      <c r="U17" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.3">
+      <c r="A18" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="0">
+        <v>260416</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="0">
+        <v>3</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="0"/>
+      <c r="G18" s="0"/>
+      <c r="H18" s="0"/>
+      <c r="I18" s="0"/>
+      <c r="J18" s="0"/>
+      <c r="K18" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="L18" s="0"/>
+      <c r="M18" s="0"/>
+      <c r="N18" s="0"/>
+      <c r="O18" s="0">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="P18" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q18" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R18" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S18" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T18" s="0"/>
+      <c r="U18" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.3">
+      <c r="A19" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="0">
+        <v>260416</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="0">
+        <v>3</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="0"/>
+      <c r="G19" s="0"/>
+      <c r="H19" s="0"/>
+      <c r="I19" s="0"/>
+      <c r="J19" s="0"/>
+      <c r="K19" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="L19" s="0"/>
+      <c r="M19" s="0"/>
+      <c r="N19" s="0"/>
+      <c r="O19" s="0">
+        <v>5</v>
+      </c>
+      <c r="P19" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q19" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R19" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S19" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T19" s="0"/>
+      <c r="U19" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.3">
+      <c r="A20" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="0">
+        <v>260416</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="0">
+        <v>3</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="0"/>
+      <c r="G20" s="0"/>
+      <c r="H20" s="0"/>
+      <c r="I20" s="0"/>
+      <c r="J20" s="0"/>
+      <c r="K20" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="0"/>
+      <c r="M20" s="0"/>
+      <c r="N20" s="0"/>
+      <c r="O20" s="0">
+        <v>10</v>
+      </c>
+      <c r="P20" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q20" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R20" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S20" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T20" s="0"/>
+      <c r="U20" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.3">
+      <c r="A21" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="0">
+        <v>260416</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" s="0">
+        <v>100</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="4">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="J21" s="4">
+        <v>1</v>
+      </c>
+      <c r="K21" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="0">
+        <v>1</v>
+      </c>
+      <c r="M21" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="N21" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O21" s="0">
+        <v>1</v>
+      </c>
+      <c r="P21" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q21" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R21" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S21" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T21" s="0"/>
+      <c r="U21" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.3">
+      <c r="A22" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="0">
+        <v>260417</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="0">
+        <v>3</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="0"/>
+      <c r="G22" s="0"/>
+      <c r="H22" s="0"/>
+      <c r="I22" s="0"/>
+      <c r="J22" s="0"/>
+      <c r="K22" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="L22" s="0"/>
+      <c r="M22" s="0"/>
+      <c r="N22" s="0"/>
+      <c r="O22" s="0">
+        <v>1</v>
+      </c>
+      <c r="P22" s="0">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
+      <c r="Q22" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="R22" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S22" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T22" s="0"/>
+      <c r="U22" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.3">
+      <c r="A23" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="0">
+        <v>260417</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="0">
+        <v>3</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="0"/>
+      <c r="G23" s="0"/>
+      <c r="H23" s="0"/>
+      <c r="I23" s="0"/>
+      <c r="J23" s="0"/>
+      <c r="K23" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="L23" s="0"/>
+      <c r="M23" s="0"/>
+      <c r="N23" s="0"/>
+      <c r="O23" s="0">
+        <v>1</v>
+      </c>
+      <c r="P23" s="0">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
+      <c r="Q23" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="R23" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S23" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T23" s="0"/>
+      <c r="U23" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.3">
+      <c r="A24" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="0">
+        <v>260417</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="0">
+        <v>3</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" s="0"/>
+      <c r="G24" s="0"/>
+      <c r="H24" s="0"/>
+      <c r="I24" s="0"/>
+      <c r="J24" s="0"/>
+      <c r="K24" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="L24" s="0"/>
+      <c r="M24" s="0"/>
+      <c r="N24" s="0"/>
+      <c r="O24" s="0">
+        <v>1</v>
+      </c>
+      <c r="P24" s="0">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="Q24" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="R24" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S24" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T24" s="0"/>
+      <c r="U24" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.3">
+      <c r="A25" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="0">
+        <v>260417</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="0">
+        <v>3</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="0"/>
+      <c r="G25" s="0"/>
+      <c r="H25" s="0"/>
+      <c r="I25" s="0"/>
+      <c r="J25" s="0"/>
+      <c r="K25" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="L25" s="0"/>
+      <c r="M25" s="0"/>
+      <c r="N25" s="0"/>
+      <c r="O25" s="0">
+        <v>1</v>
+      </c>
+      <c r="P25" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="R25" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S25" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T25" s="0"/>
+      <c r="U25" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.3">
+      <c r="A26" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="0">
+        <v>260417</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="0">
+        <v>3</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" s="0"/>
+      <c r="G26" s="0"/>
+      <c r="H26" s="0"/>
+      <c r="I26" s="0"/>
+      <c r="J26" s="0"/>
+      <c r="K26" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="L26" s="0"/>
+      <c r="M26" s="0"/>
+      <c r="N26" s="0"/>
+      <c r="O26" s="0">
+        <v>1</v>
+      </c>
+      <c r="P26" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="R26" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S26" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T26" s="0"/>
+      <c r="U26" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.3">
+      <c r="A27" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="0">
+        <v>260417</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="0">
+        <v>3</v>
+      </c>
+      <c r="E27" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" s="0"/>
+      <c r="G27" s="0"/>
+      <c r="H27" s="0"/>
+      <c r="I27" s="0"/>
+      <c r="J27" s="0"/>
+      <c r="K27" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="L27" s="0"/>
+      <c r="M27" s="0"/>
+      <c r="N27" s="0"/>
+      <c r="O27" s="0">
+        <v>1</v>
+      </c>
+      <c r="P27" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q27" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R27" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="S27" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T27" s="0"/>
+      <c r="U27" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.3">
+      <c r="A28" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="B28" s="0">
+        <v>260417</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="0">
+        <v>3</v>
+      </c>
+      <c r="E28" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" s="0"/>
+      <c r="G28" s="0"/>
+      <c r="H28" s="0"/>
+      <c r="I28" s="0"/>
+      <c r="J28" s="0"/>
+      <c r="K28" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="L28" s="0"/>
+      <c r="M28" s="0"/>
+      <c r="N28" s="0"/>
+      <c r="O28" s="0">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="P28" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q28" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R28" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="S28" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T28" s="0"/>
+      <c r="U28" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.3">
+      <c r="A29" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="0">
+        <v>260417</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="0">
+        <v>3</v>
+      </c>
+      <c r="E29" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" s="0"/>
+      <c r="G29" s="0"/>
+      <c r="H29" s="0"/>
+      <c r="I29" s="0"/>
+      <c r="J29" s="0"/>
+      <c r="K29" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="L29" s="0"/>
+      <c r="M29" s="0"/>
+      <c r="N29" s="0"/>
+      <c r="O29" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="P29" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q29" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R29" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="S29" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T29" s="0"/>
+      <c r="U29" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.3">
+      <c r="A30" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" s="0">
+        <v>260417</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="0">
+        <v>3</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F30" s="0"/>
+      <c r="G30" s="0"/>
+      <c r="H30" s="0"/>
+      <c r="I30" s="0"/>
+      <c r="J30" s="0"/>
+      <c r="K30" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="L30" s="0"/>
+      <c r="M30" s="0"/>
+      <c r="N30" s="0"/>
+      <c r="O30" s="0">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="P30" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q30" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R30" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="S30" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T30" s="0"/>
+      <c r="U30" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.3">
+      <c r="A31" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" s="0">
+        <v>260417</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="0">
+        <v>3</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F31" s="0"/>
+      <c r="G31" s="0"/>
+      <c r="H31" s="0"/>
+      <c r="I31" s="0"/>
+      <c r="J31" s="0"/>
+      <c r="K31" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="L31" s="0"/>
+      <c r="M31" s="0"/>
+      <c r="N31" s="0"/>
+      <c r="O31" s="0">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="P31" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q31" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R31" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="S31" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T31" s="0"/>
+      <c r="U31" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.3">
+      <c r="A32" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="0">
+        <v>260417</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="0">
+        <v>300</v>
+      </c>
+      <c r="E32" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" s="0">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="G32" s="0">
+        <v>0.25</v>
+      </c>
+      <c r="H32" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="I32" s="0">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="J32" s="0">
+        <v>1</v>
+      </c>
+      <c r="K32" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="L32" s="0">
+        <v>1</v>
+      </c>
+      <c r="M32" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="N32" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O32" s="0">
+        <v>1</v>
+      </c>
+      <c r="P32" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q32" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R32" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S32" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T32" s="0"/>
+      <c r="U32" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.3">
+      <c r="A33" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="0">
+        <v>260417</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" s="0">
+        <v>300</v>
+      </c>
+      <c r="E33" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="G33" s="0">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="H33" s="0">
+        <v>0</v>
+      </c>
+      <c r="I33" s="0">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="J33" s="0">
+        <v>1</v>
+      </c>
+      <c r="K33" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="L33" s="0">
+        <v>1</v>
+      </c>
+      <c r="M33" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="N33" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O33" s="0">
+        <v>1</v>
+      </c>
+      <c r="P33" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q33" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R33" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S33" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T33" s="0"/>
+      <c r="U33" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="34" x14ac:dyDescent="0.3">
+      <c r="A34" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D34" s="0">
+        <v>3</v>
+      </c>
+      <c r="E34" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F34" s="0"/>
+      <c r="G34" s="0"/>
+      <c r="H34" s="0"/>
+      <c r="I34" s="0"/>
+      <c r="J34" s="0"/>
+      <c r="K34" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="L34" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M34" s="0">
+        <v>0</v>
+      </c>
+      <c r="N34" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O34" s="0">
+        <v>1</v>
+      </c>
+      <c r="P34" s="0">
+        <v>0.001</v>
+      </c>
+      <c r="Q34" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R34" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S34" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T34" s="0"/>
+      <c r="U34" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="35" x14ac:dyDescent="0.3">
+      <c r="A35" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" s="0">
+        <v>3</v>
+      </c>
+      <c r="E35" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F35" s="0"/>
+      <c r="G35" s="0"/>
+      <c r="H35" s="0"/>
+      <c r="I35" s="0"/>
+      <c r="J35" s="0"/>
+      <c r="K35" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="L35" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M35" s="0">
+        <v>0</v>
+      </c>
+      <c r="N35" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O35" s="0">
+        <v>1</v>
+      </c>
+      <c r="P35" s="0">
+        <v>0.0050000000000000001</v>
+      </c>
+      <c r="Q35" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R35" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S35" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T35" s="0"/>
+      <c r="U35" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="36" x14ac:dyDescent="0.3">
+      <c r="A36" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D36" s="0">
+        <v>3</v>
+      </c>
+      <c r="E36" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F36" s="0"/>
+      <c r="G36" s="0"/>
+      <c r="H36" s="0"/>
+      <c r="I36" s="0"/>
+      <c r="J36" s="0"/>
+      <c r="K36" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="L36" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M36" s="0">
+        <v>0</v>
+      </c>
+      <c r="N36" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O36" s="0">
+        <v>1</v>
+      </c>
+      <c r="P36" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="Q36" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R36" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S36" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T36" s="0"/>
+      <c r="U36" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="37" x14ac:dyDescent="0.3">
+      <c r="A37" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="0">
+        <v>3</v>
+      </c>
+      <c r="E37" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F37" s="0"/>
+      <c r="G37" s="0"/>
+      <c r="H37" s="0"/>
+      <c r="I37" s="0"/>
+      <c r="J37" s="0"/>
+      <c r="K37" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="L37" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M37" s="0">
+        <v>0</v>
+      </c>
+      <c r="N37" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O37" s="0">
+        <v>1</v>
+      </c>
+      <c r="P37" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q37" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R37" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S37" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T37" s="0"/>
+      <c r="U37" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="38" x14ac:dyDescent="0.3">
+      <c r="A38" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C38" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" s="0">
+        <v>3</v>
+      </c>
+      <c r="E38" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F38" s="0"/>
+      <c r="G38" s="0"/>
+      <c r="H38" s="0"/>
+      <c r="I38" s="0"/>
+      <c r="J38" s="0"/>
+      <c r="K38" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="L38" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M38" s="0">
+        <v>0</v>
+      </c>
+      <c r="N38" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O38" s="0">
+        <v>1</v>
+      </c>
+      <c r="P38" s="0">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="Q38" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R38" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S38" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T38" s="0"/>
+      <c r="U38" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="39" x14ac:dyDescent="0.3">
+      <c r="A39" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C39" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D39" s="0">
+        <v>3</v>
+      </c>
+      <c r="E39" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F39" s="0"/>
+      <c r="G39" s="0"/>
+      <c r="H39" s="0"/>
+      <c r="I39" s="0"/>
+      <c r="J39" s="0"/>
+      <c r="K39" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="L39" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M39" s="0">
+        <v>0</v>
+      </c>
+      <c r="N39" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O39" s="0">
+        <v>1</v>
+      </c>
+      <c r="P39" s="0">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="Q39" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R39" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S39" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T39" s="0"/>
+      <c r="U39" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="40" x14ac:dyDescent="0.3">
+      <c r="A40" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C40" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D40" s="0">
+        <v>3</v>
+      </c>
+      <c r="E40" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F40" s="0"/>
+      <c r="G40" s="0"/>
+      <c r="H40" s="0"/>
+      <c r="I40" s="0"/>
+      <c r="J40" s="0"/>
+      <c r="K40" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="L40" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M40" s="0">
+        <v>0</v>
+      </c>
+      <c r="N40" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O40" s="0">
+        <v>1</v>
+      </c>
+      <c r="P40" s="0">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="Q40" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R40" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S40" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T40" s="0"/>
+      <c r="U40" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="41" x14ac:dyDescent="0.3">
+      <c r="A41" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D41" s="0">
+        <v>3</v>
+      </c>
+      <c r="E41" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F41" s="0"/>
+      <c r="G41" s="0"/>
+      <c r="H41" s="0"/>
+      <c r="I41" s="0"/>
+      <c r="J41" s="0"/>
+      <c r="K41" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="L41" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M41" s="0">
+        <v>0</v>
+      </c>
+      <c r="N41" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O41" s="0">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="P41" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q41" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R41" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S41" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T41" s="0"/>
+      <c r="U41" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="42" x14ac:dyDescent="0.3">
+      <c r="A42" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B42" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D42" s="0">
+        <v>3</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F42" s="0"/>
+      <c r="G42" s="0"/>
+      <c r="H42" s="0"/>
+      <c r="I42" s="0"/>
+      <c r="J42" s="0"/>
+      <c r="K42" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="L42" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M42" s="0">
+        <v>0</v>
+      </c>
+      <c r="N42" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O42" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="P42" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q42" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R42" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S42" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T42" s="0"/>
+      <c r="U42" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="43" x14ac:dyDescent="0.3">
+      <c r="A43" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="B43" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D43" s="0">
+        <v>3</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F43" s="0"/>
+      <c r="G43" s="0"/>
+      <c r="H43" s="0"/>
+      <c r="I43" s="0"/>
+      <c r="J43" s="0"/>
+      <c r="K43" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="L43" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M43" s="0">
+        <v>0</v>
+      </c>
+      <c r="N43" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O43" s="0">
+        <v>2</v>
+      </c>
+      <c r="P43" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q43" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R43" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S43" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T43" s="0"/>
+      <c r="U43" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="44" x14ac:dyDescent="0.3">
+      <c r="A44" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B44" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D44" s="0">
+        <v>3</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F44" s="0"/>
+      <c r="G44" s="0"/>
+      <c r="H44" s="0"/>
+      <c r="I44" s="0"/>
+      <c r="J44" s="0"/>
+      <c r="K44" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="L44" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M44" s="0">
+        <v>0</v>
+      </c>
+      <c r="N44" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O44" s="0">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="P44" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q44" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R44" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S44" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T44" s="0"/>
+      <c r="U44" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="45" x14ac:dyDescent="0.3">
+      <c r="A45" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="B45" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D45" s="0">
+        <v>3</v>
+      </c>
+      <c r="E45" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F45" s="0"/>
+      <c r="G45" s="0"/>
+      <c r="H45" s="0"/>
+      <c r="I45" s="0"/>
+      <c r="J45" s="0"/>
+      <c r="K45" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="L45" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M45" s="0">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="N45" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O45" s="0">
         <v>10</v>
       </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K8" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" t="s">
-        <v>18</v>
-      </c>
-      <c r="M8" t="s">
-        <v>19</v>
-      </c>
-      <c r="N8" t="s">
-        <v>20</v>
-      </c>
-      <c r="O8" t="s">
-        <v>21</v>
-      </c>
-      <c r="P8" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>23</v>
-      </c>
-      <c r="R8" t="s">
-        <v>24</v>
-      </c>
-      <c r="S8" t="s">
-        <v>25</v>
-      </c>
-      <c r="T8" t="s">
-        <v>26</v>
-      </c>
-      <c r="U8" t="s">
-        <v>27</v>
+      <c r="P45" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q45" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R45" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S45" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T45" s="0"/>
+      <c r="U45" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="46" x14ac:dyDescent="0.3">
+      <c r="A46" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="B46" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" s="0">
+        <v>3</v>
+      </c>
+      <c r="E46" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F46" s="0"/>
+      <c r="G46" s="0"/>
+      <c r="H46" s="0"/>
+      <c r="I46" s="0"/>
+      <c r="J46" s="0"/>
+      <c r="K46" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="L46" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M46" s="0">
+        <v>0</v>
+      </c>
+      <c r="N46" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O46" s="0">
+        <v>1</v>
+      </c>
+      <c r="P46" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="R46" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S46" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T46" s="0"/>
+      <c r="U46" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="47" x14ac:dyDescent="0.3">
+      <c r="A47" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="B47" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D47" s="0">
+        <v>3</v>
+      </c>
+      <c r="E47" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F47" s="0"/>
+      <c r="G47" s="0"/>
+      <c r="H47" s="0"/>
+      <c r="I47" s="0"/>
+      <c r="J47" s="0"/>
+      <c r="K47" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="L47" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M47" s="0">
+        <v>0</v>
+      </c>
+      <c r="N47" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O47" s="0">
+        <v>1</v>
+      </c>
+      <c r="P47" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="R47" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S47" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T47" s="0"/>
+      <c r="U47" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="48" x14ac:dyDescent="0.3">
+      <c r="A48" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B48" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48" s="0">
+        <v>3</v>
+      </c>
+      <c r="E48" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F48" s="0"/>
+      <c r="G48" s="0"/>
+      <c r="H48" s="0"/>
+      <c r="I48" s="0"/>
+      <c r="J48" s="0"/>
+      <c r="K48" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="L48" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M48" s="0">
+        <v>0</v>
+      </c>
+      <c r="N48" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O48" s="0">
+        <v>1</v>
+      </c>
+      <c r="P48" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="R48" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S48" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T48" s="0"/>
+      <c r="U48" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="49" x14ac:dyDescent="0.3">
+      <c r="A49" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D49" s="0">
+        <v>3</v>
+      </c>
+      <c r="E49" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F49" s="0"/>
+      <c r="G49" s="0"/>
+      <c r="H49" s="0"/>
+      <c r="I49" s="0"/>
+      <c r="J49" s="0"/>
+      <c r="K49" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="L49" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M49" s="0">
+        <v>0</v>
+      </c>
+      <c r="N49" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O49" s="0">
+        <v>1</v>
+      </c>
+      <c r="P49" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="R49" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S49" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T49" s="0"/>
+      <c r="U49" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="50" x14ac:dyDescent="0.3">
+      <c r="A50" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D50" s="0">
+        <v>3</v>
+      </c>
+      <c r="E50" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F50" s="0"/>
+      <c r="G50" s="0"/>
+      <c r="H50" s="0"/>
+      <c r="I50" s="0"/>
+      <c r="J50" s="0"/>
+      <c r="K50" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="L50" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M50" s="0">
+        <v>0</v>
+      </c>
+      <c r="N50" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O50" s="0">
+        <v>1</v>
+      </c>
+      <c r="P50" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="R50" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S50" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T50" s="0"/>
+      <c r="U50" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="51" x14ac:dyDescent="0.3">
+      <c r="A51" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="B51" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D51" s="0">
+        <v>3</v>
+      </c>
+      <c r="E51" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F51" s="0"/>
+      <c r="G51" s="0"/>
+      <c r="H51" s="0"/>
+      <c r="I51" s="0"/>
+      <c r="J51" s="0"/>
+      <c r="K51" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="L51" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M51" s="0">
+        <v>0</v>
+      </c>
+      <c r="N51" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O51" s="0">
+        <v>1</v>
+      </c>
+      <c r="P51" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q51" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R51" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="S51" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T51" s="0"/>
+      <c r="U51" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="52" x14ac:dyDescent="0.3">
+      <c r="A52" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="B52" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D52" s="0">
+        <v>3</v>
+      </c>
+      <c r="E52" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F52" s="0"/>
+      <c r="G52" s="0"/>
+      <c r="H52" s="0"/>
+      <c r="I52" s="0"/>
+      <c r="J52" s="0"/>
+      <c r="K52" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="L52" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M52" s="0">
+        <v>0</v>
+      </c>
+      <c r="N52" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O52" s="0">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="P52" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q52" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R52" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="S52" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T52" s="0"/>
+      <c r="U52" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="53" x14ac:dyDescent="0.3">
+      <c r="A53" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="B53" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D53" s="0">
+        <v>3</v>
+      </c>
+      <c r="E53" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F53" s="0"/>
+      <c r="G53" s="0"/>
+      <c r="H53" s="0"/>
+      <c r="I53" s="0"/>
+      <c r="J53" s="0"/>
+      <c r="K53" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="L53" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M53" s="0">
+        <v>0</v>
+      </c>
+      <c r="N53" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O53" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="P53" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q53" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R53" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="S53" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T53" s="0"/>
+      <c r="U53" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="54" x14ac:dyDescent="0.3">
+      <c r="A54" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B54" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D54" s="0">
+        <v>3</v>
+      </c>
+      <c r="E54" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F54" s="0"/>
+      <c r="G54" s="0"/>
+      <c r="H54" s="0"/>
+      <c r="I54" s="0"/>
+      <c r="J54" s="0"/>
+      <c r="K54" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="L54" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M54" s="0">
+        <v>0</v>
+      </c>
+      <c r="N54" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O54" s="0">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="P54" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q54" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R54" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="S54" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T54" s="0"/>
+      <c r="U54" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="55" x14ac:dyDescent="0.3">
+      <c r="A55" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" s="0">
+        <v>260419</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D55" s="0">
+        <v>3</v>
+      </c>
+      <c r="E55" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F55" s="0"/>
+      <c r="G55" s="0"/>
+      <c r="H55" s="0"/>
+      <c r="I55" s="0"/>
+      <c r="J55" s="0"/>
+      <c r="K55" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="L55" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="M55" s="0">
+        <v>0</v>
+      </c>
+      <c r="N55" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O55" s="0">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="P55" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="Q55" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="R55" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="S55" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T55" s="0"/>
+      <c r="U55" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="B56" s="0">
+        <v>260420</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D56" s="0">
+        <v>3</v>
+      </c>
+      <c r="E56" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F56" s="0"/>
+      <c r="G56" s="0"/>
+      <c r="H56" s="0"/>
+      <c r="I56" s="0"/>
+      <c r="J56" s="0"/>
+      <c r="K56" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="L56" s="0"/>
+      <c r="M56" s="0"/>
+      <c r="N56" s="0"/>
+      <c r="O56" s="0">
+        <v>1</v>
+      </c>
+      <c r="P56" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="R56" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="S56" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T56" s="0"/>
+      <c r="U56" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="B57" s="0">
+        <v>260420</v>
+      </c>
+      <c r="C57" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D57" s="0">
+        <v>3</v>
+      </c>
+      <c r="E57" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F57" s="0"/>
+      <c r="G57" s="0"/>
+      <c r="H57" s="0"/>
+      <c r="I57" s="0"/>
+      <c r="J57" s="0"/>
+      <c r="K57" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="L57" s="0"/>
+      <c r="M57" s="0"/>
+      <c r="N57" s="0"/>
+      <c r="O57" s="0">
+        <v>1</v>
+      </c>
+      <c r="P57" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="R57" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="S57" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T57" s="0"/>
+      <c r="U57" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="B58" s="0">
+        <v>260420</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58" s="0">
+        <v>3</v>
+      </c>
+      <c r="E58" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F58" s="0"/>
+      <c r="G58" s="0"/>
+      <c r="H58" s="0"/>
+      <c r="I58" s="0"/>
+      <c r="J58" s="0"/>
+      <c r="K58" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="L58" s="0"/>
+      <c r="M58" s="0"/>
+      <c r="N58" s="0"/>
+      <c r="O58" s="0">
+        <v>1</v>
+      </c>
+      <c r="P58" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="R58" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="S58" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T58" s="0"/>
+      <c r="U58" s="0">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/script/simulation_queue.xlsx
+++ b/script/simulation_queue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f03addda2663411/SRBL/WearableOptimizedControl/Optimizer/Moco_git/script/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="370" documentId="8_{985CFB64-8444-49E3-9649-B21738068EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF436E01-0942-470D-A8E7-948BEDE37376}"/>
+  <xr:revisionPtr revIDLastSave="423" documentId="8_{985CFB64-8444-49E3-9649-B21738068EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32906909-297F-49EF-AA95-ADB2C847CA9F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="simulation_queue" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="173">
   <si>
     <t>SF</t>
   </si>
@@ -47,13 +47,7 @@
     <t>AP</t>
   </si>
   <si>
-    <t>endheader</t>
-  </si>
-  <si>
     <t>ID</t>
-  </si>
-  <si>
-    <t>Date</t>
   </si>
   <si>
     <t>model</t>
@@ -606,6 +600,50 @@
   </si>
   <si>
     <t>abnormal</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_v1.osim</t>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_v2.osim</t>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_v3.osim</t>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_v4.osim</t>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_v5.osim</t>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_v6.osim</t>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_v7.osim</t>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_v8.osim</t>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_v9.osim</t>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_v10.osim</t>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_v11.osim</t>
+  </si>
+  <si>
+    <t>260423</t>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_v1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_v2.osim</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1570,12 +1608,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.75" customWidth="1"/>
     <col min="2" max="2" width="10.625" customWidth="1"/>
-    <col min="3" max="3" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="21.5" customWidth="1"/>
     <col min="4" max="4" width="11.75" customWidth="1"/>
     <col min="5" max="5" width="13.5" customWidth="1"/>
     <col min="6" max="6" width="6.875" customWidth="1"/>
@@ -1598,7 +1636,7 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B1" s="2">
         <v>0.01</v>
@@ -1606,7 +1644,7 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2">
         <v>0</v>
@@ -1614,7 +1652,7 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -1622,7 +1660,7 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2">
         <v>0.03</v>
@@ -1630,117 +1668,337 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="165" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B9" s="2"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>6</v>
+        <v>151</v>
       </c>
       <c r="B10" s="2"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="D11" t="s">
         <v>8</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
         <v>9</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>10</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>11</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H11" t="s">
         <v>12</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
         <v>13</v>
       </c>
-      <c r="H11" t="s">
+      <c r="J11" t="s">
         <v>14</v>
       </c>
-      <c r="I11" t="s">
+      <c r="K11" t="s">
         <v>15</v>
       </c>
-      <c r="J11" t="s">
+      <c r="L11" t="s">
         <v>16</v>
       </c>
-      <c r="K11" t="s">
+      <c r="M11" t="s">
         <v>17</v>
       </c>
-      <c r="L11" t="s">
+      <c r="N11" t="s">
         <v>18</v>
       </c>
-      <c r="M11" t="s">
+      <c r="O11" t="s">
         <v>19</v>
       </c>
-      <c r="N11" t="s">
+      <c r="P11" t="s">
         <v>20</v>
       </c>
-      <c r="O11" t="s">
+      <c r="Q11" t="s">
         <v>21</v>
       </c>
-      <c r="P11" t="s">
+      <c r="R11" t="s">
         <v>22</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="S11" t="s">
         <v>23</v>
       </c>
-      <c r="R11" t="s">
+      <c r="T11" t="s">
         <v>24</v>
       </c>
-      <c r="S11" t="s">
+      <c r="U11" t="s">
         <v>25</v>
       </c>
-      <c r="T11" t="s">
-        <v>26</v>
-      </c>
-      <c r="U11" t="s">
-        <v>27</v>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>260423</v>
+      </c>
+      <c r="C12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12" t="s">
+        <v>36</v>
+      </c>
+      <c r="S12" t="s">
+        <v>27</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>260423</v>
+      </c>
+      <c r="C13" t="s">
+        <v>172</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S13" t="s">
+        <v>27</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>260423</v>
+      </c>
+      <c r="C14" t="s">
+        <v>161</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14" t="s">
+        <v>36</v>
+      </c>
+      <c r="S14" t="s">
+        <v>27</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>260423</v>
+      </c>
+      <c r="C15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S15" t="s">
+        <v>27</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>260423</v>
+      </c>
+      <c r="C16" t="s">
+        <v>163</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16" t="s">
+        <v>36</v>
+      </c>
+      <c r="S16" t="s">
+        <v>27</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>260423</v>
+      </c>
+      <c r="C17" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17" t="s">
+        <v>36</v>
+      </c>
+      <c r="S17" t="s">
+        <v>27</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>260423</v>
+      </c>
+      <c r="C18" t="s">
+        <v>165</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18" t="s">
+        <v>36</v>
+      </c>
+      <c r="S18" t="s">
+        <v>27</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <v>260423</v>
+      </c>
+      <c r="C19" t="s">
+        <v>166</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19" t="s">
+        <v>36</v>
+      </c>
+      <c r="S19" t="s">
+        <v>27</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>260423</v>
+      </c>
+      <c r="C20" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20" t="s">
+        <v>36</v>
+      </c>
+      <c r="S20" t="s">
+        <v>27</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>260423</v>
+      </c>
+      <c r="C21" t="s">
+        <v>168</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21" t="s">
+        <v>36</v>
+      </c>
+      <c r="S21" t="s">
+        <v>27</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>260423</v>
+      </c>
+      <c r="C22" t="s">
+        <v>169</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22" t="s">
+        <v>36</v>
+      </c>
+      <c r="S22" t="s">
+        <v>27</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1826,92 +2084,92 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>9</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>10</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>12</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>13</v>
       </c>
-      <c r="H8" t="s">
+      <c r="J8" t="s">
         <v>14</v>
       </c>
-      <c r="I8" t="s">
+      <c r="K8" t="s">
         <v>15</v>
       </c>
-      <c r="J8" t="s">
+      <c r="L8" t="s">
         <v>16</v>
       </c>
-      <c r="K8" t="s">
+      <c r="M8" t="s">
         <v>17</v>
       </c>
-      <c r="L8" t="s">
+      <c r="N8" t="s">
         <v>18</v>
       </c>
-      <c r="M8" t="s">
+      <c r="O8" t="s">
         <v>19</v>
       </c>
-      <c r="N8" t="s">
+      <c r="P8" t="s">
         <v>20</v>
       </c>
-      <c r="O8" t="s">
+      <c r="Q8" t="s">
         <v>21</v>
       </c>
-      <c r="P8" t="s">
+      <c r="R8" t="s">
         <v>22</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="S8" t="s">
         <v>23</v>
       </c>
-      <c r="R8" t="s">
+      <c r="T8" t="s">
         <v>24</v>
       </c>
-      <c r="S8" t="s">
+      <c r="U8" t="s">
         <v>25</v>
-      </c>
-      <c r="T8" t="s">
-        <v>26</v>
-      </c>
-      <c r="U8" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>260416</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O9">
         <v>1</v>
@@ -1920,13 +2178,13 @@
         <v>1E-3</v>
       </c>
       <c r="Q9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U9">
         <v>1</v>
@@ -1934,22 +2192,22 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>260416</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="O10">
         <v>1</v>
@@ -1958,13 +2216,13 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U10">
         <v>1</v>
@@ -1972,22 +2230,22 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>260416</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O11">
         <v>1</v>
@@ -1996,13 +2254,13 @@
         <v>0.01</v>
       </c>
       <c r="Q11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U11">
         <v>1</v>
@@ -2010,22 +2268,22 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>260416</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O12">
         <v>1</v>
@@ -2034,13 +2292,13 @@
         <v>0.03</v>
       </c>
       <c r="Q12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U12">
         <v>1</v>
@@ -2048,22 +2306,22 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>260416</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="O13">
         <v>1</v>
@@ -2072,13 +2330,13 @@
         <v>0.05</v>
       </c>
       <c r="Q13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U13">
         <v>1</v>
@@ -2086,22 +2344,22 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B14">
         <v>260416</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O14">
         <v>1</v>
@@ -2110,13 +2368,13 @@
         <v>0.1</v>
       </c>
       <c r="Q14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U14">
         <v>1</v>
@@ -2124,22 +2382,22 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>260416</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D15">
         <v>3</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="O15">
         <v>1</v>
@@ -2148,13 +2406,13 @@
         <v>0.3</v>
       </c>
       <c r="Q15" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U15">
         <v>1</v>
@@ -2162,22 +2420,22 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B16">
         <v>260416</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D16">
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="O16">
         <v>0.1</v>
@@ -2186,13 +2444,13 @@
         <v>0.03</v>
       </c>
       <c r="Q16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U16">
         <v>1</v>
@@ -2200,22 +2458,22 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>260416</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D17">
         <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="O17">
         <v>0.5</v>
@@ -2224,13 +2482,13 @@
         <v>0.03</v>
       </c>
       <c r="Q17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U17">
         <v>1</v>
@@ -2238,22 +2496,22 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>260416</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D18">
         <v>3</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O18">
         <v>2</v>
@@ -2262,13 +2520,13 @@
         <v>0.03</v>
       </c>
       <c r="Q18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U18">
         <v>1</v>
@@ -2276,22 +2534,22 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B19">
         <v>260416</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D19">
         <v>3</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O19">
         <v>5</v>
@@ -2300,13 +2558,13 @@
         <v>0.03</v>
       </c>
       <c r="Q19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U19">
         <v>1</v>
@@ -2314,22 +2572,22 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B20">
         <v>260416</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D20">
         <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O20">
         <v>10</v>
@@ -2338,13 +2596,13 @@
         <v>0.03</v>
       </c>
       <c r="Q20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U20">
         <v>1</v>
@@ -2352,19 +2610,19 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B21">
         <v>260416</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D21">
         <v>100</v>
       </c>
       <c r="E21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F21" s="4">
         <v>0.1</v>
@@ -2382,7 +2640,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L21">
         <v>1</v>
@@ -2391,7 +2649,7 @@
         <v>0.03</v>
       </c>
       <c r="N21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O21">
         <v>1</v>
@@ -2400,13 +2658,13 @@
         <v>0.03</v>
       </c>
       <c r="Q21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U21">
         <v>1</v>
@@ -2414,22 +2672,22 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B22">
         <v>260417</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D22">
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K22" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O22">
         <v>1</v>
@@ -2438,13 +2696,13 @@
         <v>0</v>
       </c>
       <c r="Q22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="R22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U22">
         <v>1</v>
@@ -2452,22 +2710,22 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B23">
         <v>260417</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D23">
         <v>3</v>
       </c>
       <c r="E23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O23">
         <v>1</v>
@@ -2476,13 +2734,13 @@
         <v>0</v>
       </c>
       <c r="Q23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="R23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U23">
         <v>1</v>
@@ -2490,22 +2748,22 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B24">
         <v>260417</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D24">
         <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K24" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O24">
         <v>1</v>
@@ -2514,13 +2772,13 @@
         <v>0</v>
       </c>
       <c r="Q24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="R24" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S24" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U24">
         <v>1</v>
@@ -2528,22 +2786,22 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B25">
         <v>260417</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D25">
         <v>3</v>
       </c>
       <c r="E25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="O25">
         <v>1</v>
@@ -2552,13 +2810,13 @@
         <v>0</v>
       </c>
       <c r="Q25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R25" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S25" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U25">
         <v>1</v>
@@ -2566,22 +2824,22 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B26">
         <v>260417</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D26">
         <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O26">
         <v>1</v>
@@ -2590,13 +2848,13 @@
         <v>0</v>
       </c>
       <c r="Q26" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="R26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U26">
         <v>1</v>
@@ -2604,22 +2862,22 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B27">
         <v>260417</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D27">
         <v>3</v>
       </c>
       <c r="E27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O27">
         <v>1</v>
@@ -2628,13 +2886,13 @@
         <v>0.03</v>
       </c>
       <c r="Q27" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R27" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="S27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U27">
         <v>1</v>
@@ -2642,22 +2900,22 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B28">
         <v>260417</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D28">
         <v>3</v>
       </c>
       <c r="E28" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O28">
         <v>0.7</v>
@@ -2666,13 +2924,13 @@
         <v>0.03</v>
       </c>
       <c r="Q28" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="S28" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U28">
         <v>1</v>
@@ -2680,22 +2938,22 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B29">
         <v>260417</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D29">
         <v>3</v>
       </c>
       <c r="E29" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O29">
         <v>0.5</v>
@@ -2704,13 +2962,13 @@
         <v>0.03</v>
       </c>
       <c r="Q29" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R29" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="S29" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U29">
         <v>1</v>
@@ -2718,22 +2976,22 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B30">
         <v>260417</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D30">
         <v>3</v>
       </c>
       <c r="E30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K30" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="O30">
         <v>0.3</v>
@@ -2742,13 +3000,13 @@
         <v>0.03</v>
       </c>
       <c r="Q30" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="S30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U30">
         <v>1</v>
@@ -2756,22 +3014,22 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B31">
         <v>260417</v>
       </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D31">
         <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K31" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O31">
         <v>0.1</v>
@@ -2780,13 +3038,13 @@
         <v>0.03</v>
       </c>
       <c r="Q31" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R31" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="S31" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U31">
         <v>1</v>
@@ -2794,19 +3052,19 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B32">
         <v>260417</v>
       </c>
       <c r="C32" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D32">
         <v>300</v>
       </c>
       <c r="E32" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F32">
         <v>0.1</v>
@@ -2824,7 +3082,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L32">
         <v>1</v>
@@ -2833,7 +3091,7 @@
         <v>0.03</v>
       </c>
       <c r="N32" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O32">
         <v>1</v>
@@ -2842,13 +3100,13 @@
         <v>0.03</v>
       </c>
       <c r="Q32" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R32" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S32" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U32">
         <v>1</v>
@@ -2856,19 +3114,19 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B33">
         <v>260417</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D33">
         <v>300</v>
       </c>
       <c r="E33" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F33">
         <v>0.2</v>
@@ -2886,7 +3144,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L33">
         <v>1</v>
@@ -2895,7 +3153,7 @@
         <v>0.03</v>
       </c>
       <c r="N33" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O33">
         <v>1</v>
@@ -2904,13 +3162,13 @@
         <v>0.03</v>
       </c>
       <c r="Q33" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R33" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S33" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U33">
         <v>1</v>
@@ -2918,22 +3176,22 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B34">
         <v>260419</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D34">
         <v>3</v>
       </c>
       <c r="E34" t="s">
+        <v>77</v>
+      </c>
+      <c r="K34" t="s">
         <v>79</v>
-      </c>
-      <c r="K34" t="s">
-        <v>81</v>
       </c>
       <c r="L34">
         <v>0.01</v>
@@ -2942,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O34">
         <v>1</v>
@@ -2951,13 +3209,13 @@
         <v>1E-3</v>
       </c>
       <c r="Q34" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R34" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S34" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U34">
         <v>1</v>
@@ -2965,22 +3223,22 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B35">
         <v>260419</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D35">
         <v>3</v>
       </c>
       <c r="E35" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K35" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L35">
         <v>0.01</v>
@@ -2989,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O35">
         <v>1</v>
@@ -2998,13 +3256,13 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q35" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R35" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S35" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U35">
         <v>1</v>
@@ -3012,22 +3270,22 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B36">
         <v>260419</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D36">
         <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K36" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L36">
         <v>0.01</v>
@@ -3036,7 +3294,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O36">
         <v>1</v>
@@ -3045,13 +3303,13 @@
         <v>0.01</v>
       </c>
       <c r="Q36" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R36" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S36" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U36">
         <v>1</v>
@@ -3059,22 +3317,22 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B37">
         <v>260419</v>
       </c>
       <c r="C37" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D37">
         <v>3</v>
       </c>
       <c r="E37" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K37" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L37">
         <v>0.01</v>
@@ -3083,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="N37" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O37">
         <v>1</v>
@@ -3092,13 +3350,13 @@
         <v>0.03</v>
       </c>
       <c r="Q37" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R37" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S37" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U37">
         <v>1</v>
@@ -3106,22 +3364,22 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B38">
         <v>260419</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D38">
         <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K38" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L38">
         <v>0.01</v>
@@ -3130,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="N38" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O38">
         <v>1</v>
@@ -3139,13 +3397,13 @@
         <v>0.05</v>
       </c>
       <c r="Q38" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R38" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S38" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U38">
         <v>1</v>
@@ -3153,22 +3411,22 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B39">
         <v>260419</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D39">
         <v>3</v>
       </c>
       <c r="E39" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K39" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L39">
         <v>0.01</v>
@@ -3177,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O39">
         <v>1</v>
@@ -3186,13 +3444,13 @@
         <v>0.1</v>
       </c>
       <c r="Q39" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R39" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S39" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U39">
         <v>1</v>
@@ -3200,22 +3458,22 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B40">
         <v>260419</v>
       </c>
       <c r="C40" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D40">
         <v>3</v>
       </c>
       <c r="E40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L40">
         <v>0.01</v>
@@ -3224,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="N40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O40">
         <v>1</v>
@@ -3233,13 +3491,13 @@
         <v>0.3</v>
       </c>
       <c r="Q40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R40" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S40" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U40">
         <v>1</v>
@@ -3247,22 +3505,22 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B41">
         <v>260419</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D41">
         <v>3</v>
       </c>
       <c r="E41" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K41" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L41">
         <v>0.01</v>
@@ -3271,7 +3529,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O41">
         <v>0.1</v>
@@ -3280,13 +3538,13 @@
         <v>0.03</v>
       </c>
       <c r="Q41" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R41" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S41" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U41">
         <v>1</v>
@@ -3294,22 +3552,22 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B42">
         <v>260419</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D42">
         <v>3</v>
       </c>
       <c r="E42" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L42">
         <v>0.01</v>
@@ -3318,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="N42" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O42">
         <v>0.5</v>
@@ -3327,13 +3585,13 @@
         <v>0.03</v>
       </c>
       <c r="Q42" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R42" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S42" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U42">
         <v>1</v>
@@ -3341,22 +3599,22 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B43">
         <v>260419</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D43">
         <v>3</v>
       </c>
       <c r="E43" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K43" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L43">
         <v>0.01</v>
@@ -3365,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O43">
         <v>2</v>
@@ -3374,13 +3632,13 @@
         <v>0.03</v>
       </c>
       <c r="Q43" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R43" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S43" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U43">
         <v>1</v>
@@ -3388,22 +3646,22 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B44">
         <v>260419</v>
       </c>
       <c r="C44" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D44">
         <v>3</v>
       </c>
       <c r="E44" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K44" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L44">
         <v>0.01</v>
@@ -3412,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O44">
         <v>5</v>
@@ -3421,13 +3679,13 @@
         <v>0.03</v>
       </c>
       <c r="Q44" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R44" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S44" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U44">
         <v>1</v>
@@ -3435,22 +3693,22 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B45">
         <v>260419</v>
       </c>
       <c r="C45" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D45">
         <v>3</v>
       </c>
       <c r="E45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K45" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L45">
         <v>0.01</v>
@@ -3459,7 +3717,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O45">
         <v>10</v>
@@ -3468,13 +3726,13 @@
         <v>0.03</v>
       </c>
       <c r="Q45" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R45" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S45" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U45">
         <v>1</v>
@@ -3482,22 +3740,22 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B46">
         <v>260419</v>
       </c>
       <c r="C46" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D46">
         <v>3</v>
       </c>
       <c r="E46" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K46" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L46">
         <v>0.01</v>
@@ -3506,7 +3764,7 @@
         <v>0</v>
       </c>
       <c r="N46" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O46">
         <v>1</v>
@@ -3515,13 +3773,13 @@
         <v>0</v>
       </c>
       <c r="Q46" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="R46" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S46" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U46">
         <v>1</v>
@@ -3529,22 +3787,22 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B47">
         <v>260419</v>
       </c>
       <c r="C47" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D47">
         <v>3</v>
       </c>
       <c r="E47" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K47" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L47">
         <v>0.01</v>
@@ -3553,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="N47" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O47">
         <v>1</v>
@@ -3562,13 +3820,13 @@
         <v>0</v>
       </c>
       <c r="Q47" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="R47" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S47" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U47">
         <v>1</v>
@@ -3576,22 +3834,22 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B48">
         <v>260419</v>
       </c>
       <c r="C48" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D48">
         <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K48" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L48">
         <v>0.01</v>
@@ -3600,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="N48" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O48">
         <v>1</v>
@@ -3609,13 +3867,13 @@
         <v>0</v>
       </c>
       <c r="Q48" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="R48" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S48" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U48">
         <v>1</v>
@@ -3623,22 +3881,22 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B49">
         <v>260419</v>
       </c>
       <c r="C49" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D49">
         <v>3</v>
       </c>
       <c r="E49" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K49" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L49">
         <v>0.01</v>
@@ -3647,7 +3905,7 @@
         <v>0</v>
       </c>
       <c r="N49" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O49">
         <v>1</v>
@@ -3656,13 +3914,13 @@
         <v>0</v>
       </c>
       <c r="Q49" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R49" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S49" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U49">
         <v>1</v>
@@ -3670,22 +3928,22 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B50">
         <v>260419</v>
       </c>
       <c r="C50" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D50">
         <v>3</v>
       </c>
       <c r="E50" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K50" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L50">
         <v>0.01</v>
@@ -3694,7 +3952,7 @@
         <v>0</v>
       </c>
       <c r="N50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O50">
         <v>1</v>
@@ -3703,13 +3961,13 @@
         <v>0</v>
       </c>
       <c r="Q50" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="R50" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S50" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U50">
         <v>1</v>
@@ -3717,22 +3975,22 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B51">
         <v>260419</v>
       </c>
       <c r="C51" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D51">
         <v>3</v>
       </c>
       <c r="E51" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K51" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L51">
         <v>0.01</v>
@@ -3741,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="N51" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O51">
         <v>1</v>
@@ -3750,13 +4008,13 @@
         <v>0.03</v>
       </c>
       <c r="Q51" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R51" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="S51" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U51">
         <v>1</v>
@@ -3764,22 +4022,22 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B52">
         <v>260419</v>
       </c>
       <c r="C52" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D52">
         <v>3</v>
       </c>
       <c r="E52" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K52" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L52">
         <v>0.01</v>
@@ -3788,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="N52" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O52">
         <v>0.7</v>
@@ -3797,13 +4055,13 @@
         <v>0.03</v>
       </c>
       <c r="Q52" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R52" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="S52" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U52">
         <v>1</v>
@@ -3811,22 +4069,22 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B53">
         <v>260419</v>
       </c>
       <c r="C53" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D53">
         <v>3</v>
       </c>
       <c r="E53" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K53" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L53">
         <v>0.01</v>
@@ -3835,7 +4093,7 @@
         <v>0</v>
       </c>
       <c r="N53" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O53">
         <v>0.5</v>
@@ -3844,13 +4102,13 @@
         <v>0.03</v>
       </c>
       <c r="Q53" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R53" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="S53" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U53">
         <v>1</v>
@@ -3858,22 +4116,22 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B54">
         <v>260419</v>
       </c>
       <c r="C54" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D54">
         <v>3</v>
       </c>
       <c r="E54" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K54" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L54">
         <v>0.01</v>
@@ -3882,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="N54" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O54">
         <v>0.3</v>
@@ -3891,13 +4149,13 @@
         <v>0.03</v>
       </c>
       <c r="Q54" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R54" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="S54" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U54">
         <v>1</v>
@@ -3905,22 +4163,22 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B55">
         <v>260419</v>
       </c>
       <c r="C55" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D55">
         <v>3</v>
       </c>
       <c r="E55" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K55" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L55">
         <v>0.01</v>
@@ -3929,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="N55" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O55">
         <v>0.1</v>
@@ -3938,13 +4196,13 @@
         <v>0.03</v>
       </c>
       <c r="Q55" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R55" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="S55" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U55">
         <v>1</v>
@@ -3952,22 +4210,22 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B56">
         <v>260420</v>
       </c>
       <c r="C56" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D56">
         <v>3</v>
       </c>
       <c r="E56" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K56" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O56">
         <v>1</v>
@@ -3976,13 +4234,13 @@
         <v>0</v>
       </c>
       <c r="Q56" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="R56" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="S56" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U56">
         <v>1</v>
@@ -3990,22 +4248,22 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B57">
         <v>260420</v>
       </c>
       <c r="C57" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D57">
         <v>3</v>
       </c>
       <c r="E57" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K57" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="O57">
         <v>1</v>
@@ -4014,13 +4272,13 @@
         <v>0</v>
       </c>
       <c r="Q57" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="R57" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="S57" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U57">
         <v>1</v>
@@ -4028,22 +4286,22 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B58">
         <v>260420</v>
       </c>
       <c r="C58" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D58">
         <v>3</v>
       </c>
       <c r="E58" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K58" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O58">
         <v>1</v>
@@ -4052,13 +4310,13 @@
         <v>0</v>
       </c>
       <c r="Q58" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="R58" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="S58" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U58">
         <v>1</v>
@@ -4066,22 +4324,22 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B59">
         <v>260421</v>
       </c>
       <c r="C59" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D59">
         <v>3</v>
       </c>
       <c r="E59" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K59" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O59">
         <v>1</v>
@@ -4090,13 +4348,13 @@
         <v>0.1</v>
       </c>
       <c r="Q59" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R59" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S59" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U59">
         <v>1</v>
@@ -4104,22 +4362,22 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B60">
         <v>260421</v>
       </c>
       <c r="C60" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D60">
         <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K60" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O60">
         <v>1</v>
@@ -4128,13 +4386,13 @@
         <v>0.2</v>
       </c>
       <c r="Q60" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R60" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S60" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U60">
         <v>1</v>
@@ -4142,22 +4400,22 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B61">
         <v>260421</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D61">
         <v>3</v>
       </c>
       <c r="E61" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K61" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="O61">
         <v>1</v>
@@ -4166,13 +4424,13 @@
         <v>0.3</v>
       </c>
       <c r="Q61" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R61" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S61" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U61">
         <v>1</v>
@@ -4180,22 +4438,22 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B62">
         <v>260421</v>
       </c>
       <c r="C62" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D62">
         <v>3</v>
       </c>
       <c r="E62" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K62" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O62">
         <v>1</v>
@@ -4204,13 +4462,13 @@
         <v>0.4</v>
       </c>
       <c r="Q62" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R62" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S62" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U62">
         <v>1</v>
@@ -4218,22 +4476,22 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B63">
         <v>260421</v>
       </c>
       <c r="C63" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D63">
         <v>3</v>
       </c>
       <c r="E63" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="O63">
         <v>1</v>
@@ -4242,13 +4500,13 @@
         <v>0.5</v>
       </c>
       <c r="Q63" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R63" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S63" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U63">
         <v>1</v>
@@ -4256,22 +4514,22 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B64">
         <v>260421</v>
       </c>
       <c r="C64" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D64">
         <v>3</v>
       </c>
       <c r="E64" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K64" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O64">
         <v>1</v>
@@ -4280,13 +4538,13 @@
         <v>0.7</v>
       </c>
       <c r="Q64" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R64" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S64" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U64">
         <v>1</v>
@@ -4294,37 +4552,37 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B65">
         <v>260421</v>
       </c>
       <c r="C65" t="s">
+        <v>26</v>
+      </c>
+      <c r="D65">
+        <v>3</v>
+      </c>
+      <c r="E65" t="s">
+        <v>36</v>
+      </c>
+      <c r="K65" t="s">
+        <v>116</v>
+      </c>
+      <c r="O65">
+        <v>1</v>
+      </c>
+      <c r="P65">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>66</v>
+      </c>
+      <c r="R65" t="s">
         <v>28</v>
       </c>
-      <c r="D65">
-        <v>3</v>
-      </c>
-      <c r="E65" t="s">
-        <v>38</v>
-      </c>
-      <c r="K65" t="s">
-        <v>118</v>
-      </c>
-      <c r="O65">
-        <v>1</v>
-      </c>
-      <c r="P65">
-        <v>1</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>68</v>
-      </c>
-      <c r="R65" t="s">
-        <v>30</v>
-      </c>
       <c r="S65" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U65">
         <v>1</v>
@@ -4332,22 +4590,22 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B66">
         <v>260421</v>
       </c>
       <c r="C66" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D66">
         <v>3</v>
       </c>
       <c r="E66" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K66" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O66">
         <v>1</v>
@@ -4356,13 +4614,13 @@
         <v>1.5</v>
       </c>
       <c r="Q66" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R66" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S66" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U66">
         <v>1</v>
@@ -4370,22 +4628,22 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B67">
         <v>260421</v>
       </c>
       <c r="C67" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D67">
         <v>3</v>
       </c>
       <c r="E67" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K67" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="O67">
         <v>1</v>
@@ -4394,13 +4652,13 @@
         <v>2</v>
       </c>
       <c r="Q67" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R67" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S67" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U67">
         <v>1</v>
@@ -4408,22 +4666,22 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B68">
         <v>260421</v>
       </c>
       <c r="C68" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D68">
         <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K68" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="O68">
         <v>1</v>
@@ -4432,13 +4690,13 @@
         <v>1E-3</v>
       </c>
       <c r="Q68" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R68" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S68" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U68">
         <v>1</v>
@@ -4446,22 +4704,22 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B69">
         <v>260421</v>
       </c>
       <c r="C69" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D69">
         <v>3</v>
       </c>
       <c r="E69" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K69" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="O69">
         <v>1</v>
@@ -4470,13 +4728,13 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="Q69" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R69" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S69" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U69">
         <v>1</v>
@@ -4484,22 +4742,22 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B70">
         <v>260421</v>
       </c>
       <c r="C70" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D70">
         <v>3</v>
       </c>
       <c r="E70" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K70" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O70">
         <v>1</v>
@@ -4508,13 +4766,13 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q70" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R70" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S70" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U70">
         <v>1</v>
@@ -4522,22 +4780,22 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B71">
         <v>260421</v>
       </c>
       <c r="C71" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D71">
         <v>3</v>
       </c>
       <c r="E71" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K71" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="O71">
         <v>1</v>
@@ -4546,13 +4804,13 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="Q71" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R71" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S71" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U71">
         <v>1</v>
@@ -4560,22 +4818,22 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B72">
         <v>260421</v>
       </c>
       <c r="C72" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D72">
         <v>3</v>
       </c>
       <c r="E72" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K72" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="O72">
         <v>1</v>
@@ -4584,13 +4842,13 @@
         <v>0.01</v>
       </c>
       <c r="Q72" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R72" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S72" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U72">
         <v>1</v>
@@ -4598,22 +4856,22 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B73">
         <v>260421</v>
       </c>
       <c r="C73" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D73">
         <v>3</v>
       </c>
       <c r="E73" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K73" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="O73">
         <v>1</v>
@@ -4622,13 +4880,13 @@
         <v>0.03</v>
       </c>
       <c r="Q73" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R73" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S73" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U73">
         <v>1</v>
@@ -4636,22 +4894,22 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B74">
         <v>260421</v>
       </c>
       <c r="C74" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D74">
         <v>3</v>
       </c>
       <c r="E74" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K74" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O74">
         <v>1</v>
@@ -4660,13 +4918,13 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="Q74" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R74" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S74" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U74">
         <v>1</v>
@@ -4674,22 +4932,22 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B75">
         <v>260421</v>
       </c>
       <c r="C75" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D75">
         <v>3</v>
       </c>
       <c r="E75" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K75" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O75">
         <v>1</v>
@@ -4698,13 +4956,13 @@
         <v>0.1</v>
       </c>
       <c r="Q75" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R75" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S75" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U75">
         <v>1</v>
@@ -4712,22 +4970,22 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B76">
         <v>260421</v>
       </c>
       <c r="C76" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D76">
         <v>3</v>
       </c>
       <c r="E76" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K76" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="O76">
         <v>1</v>
@@ -4736,13 +4994,13 @@
         <v>0.3</v>
       </c>
       <c r="Q76" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R76" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S76" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U76">
         <v>1</v>
@@ -4750,22 +5008,22 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B77">
         <v>260421</v>
       </c>
       <c r="C77" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D77">
         <v>3</v>
       </c>
       <c r="E77" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K77" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O77">
         <v>1</v>
@@ -4774,13 +5032,13 @@
         <v>0.5</v>
       </c>
       <c r="Q77" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R77" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S77" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U77">
         <v>1</v>
@@ -4788,22 +5046,22 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B78">
         <v>260421</v>
       </c>
       <c r="C78" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D78">
         <v>3</v>
       </c>
       <c r="E78" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K78" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="O78">
         <v>1</v>
@@ -4812,13 +5070,13 @@
         <v>0.7</v>
       </c>
       <c r="Q78" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R78" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S78" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U78">
         <v>1</v>
@@ -4826,37 +5084,37 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B79">
         <v>260421</v>
       </c>
       <c r="C79" t="s">
+        <v>26</v>
+      </c>
+      <c r="D79">
+        <v>3</v>
+      </c>
+      <c r="E79" t="s">
+        <v>36</v>
+      </c>
+      <c r="K79" t="s">
+        <v>130</v>
+      </c>
+      <c r="O79">
+        <v>1</v>
+      </c>
+      <c r="P79">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>112</v>
+      </c>
+      <c r="R79" t="s">
         <v>28</v>
       </c>
-      <c r="D79">
-        <v>3</v>
-      </c>
-      <c r="E79" t="s">
-        <v>38</v>
-      </c>
-      <c r="K79" t="s">
-        <v>132</v>
-      </c>
-      <c r="O79">
-        <v>1</v>
-      </c>
-      <c r="P79">
-        <v>1</v>
-      </c>
-      <c r="Q79" t="s">
-        <v>114</v>
-      </c>
-      <c r="R79" t="s">
-        <v>30</v>
-      </c>
       <c r="S79" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U79">
         <v>1</v>
@@ -4864,22 +5122,22 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B80">
         <v>260421</v>
       </c>
       <c r="C80" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D80">
         <v>3</v>
       </c>
       <c r="E80" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K80" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="O80">
         <v>1</v>
@@ -4888,13 +5146,13 @@
         <v>1.5</v>
       </c>
       <c r="Q80" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R80" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S80" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U80">
         <v>1</v>
@@ -4902,22 +5160,22 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B81">
         <v>260421</v>
       </c>
       <c r="C81" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D81">
         <v>3</v>
       </c>
       <c r="E81" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K81" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="O81">
         <v>1</v>
@@ -4926,13 +5184,13 @@
         <v>2</v>
       </c>
       <c r="Q81" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R81" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S81" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U81">
         <v>1</v>
@@ -4940,22 +5198,22 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B82">
         <v>260421</v>
       </c>
       <c r="C82" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D82">
         <v>3</v>
       </c>
       <c r="E82" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K82" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O82">
         <v>1</v>
@@ -4964,13 +5222,13 @@
         <v>0.03</v>
       </c>
       <c r="Q82" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R82" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S82" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U82">
         <v>1</v>
@@ -4978,22 +5236,22 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B83">
         <v>260421</v>
       </c>
       <c r="C83" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D83">
         <v>3</v>
       </c>
       <c r="E83" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K83" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O83">
         <v>1</v>
@@ -5002,13 +5260,13 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="Q83" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R83" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S83" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U83">
         <v>1</v>
@@ -5016,22 +5274,22 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B84">
         <v>260421</v>
       </c>
       <c r="C84" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D84">
         <v>3</v>
       </c>
       <c r="E84" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K84" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="O84">
         <v>1</v>
@@ -5040,13 +5298,13 @@
         <v>0.1</v>
       </c>
       <c r="Q84" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R84" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S84" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U84">
         <v>1</v>
@@ -5054,22 +5312,22 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B85">
         <v>260421</v>
       </c>
       <c r="C85" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D85">
         <v>3</v>
       </c>
       <c r="E85" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K85" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O85">
         <v>1</v>
@@ -5078,13 +5336,13 @@
         <v>1E-3</v>
       </c>
       <c r="Q85" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R85" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S85" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U85">
         <v>1</v>
@@ -5092,22 +5350,22 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B86">
         <v>260421</v>
       </c>
       <c r="C86" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D86">
         <v>3</v>
       </c>
       <c r="E86" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K86" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O86">
         <v>1</v>
@@ -5116,13 +5374,13 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="Q86" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R86" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S86" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U86">
         <v>1</v>
@@ -5130,22 +5388,22 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B87">
         <v>260421</v>
       </c>
       <c r="C87" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D87">
         <v>3</v>
       </c>
       <c r="E87" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K87" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O87">
         <v>1</v>
@@ -5154,13 +5412,13 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q87" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R87" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S87" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U87">
         <v>1</v>
@@ -5168,22 +5426,22 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B88">
         <v>260421</v>
       </c>
       <c r="C88" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D88">
         <v>3</v>
       </c>
       <c r="E88" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K88" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="O88">
         <v>1</v>
@@ -5192,13 +5450,13 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="Q88" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R88" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S88" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U88">
         <v>1</v>
@@ -5206,22 +5464,22 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B89">
         <v>260421</v>
       </c>
       <c r="C89" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D89">
         <v>3</v>
       </c>
       <c r="E89" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K89" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="O89">
         <v>1</v>
@@ -5230,13 +5488,13 @@
         <v>0.01</v>
       </c>
       <c r="Q89" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R89" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S89" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U89">
         <v>1</v>
@@ -5244,22 +5502,22 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B90">
         <v>260421</v>
       </c>
       <c r="C90" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D90">
         <v>3</v>
       </c>
       <c r="E90" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K90" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O90">
         <v>1</v>
@@ -5268,13 +5526,13 @@
         <v>0.03</v>
       </c>
       <c r="Q90" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R90" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S90" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U90">
         <v>1</v>
@@ -5282,22 +5540,22 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B91">
         <v>260421</v>
       </c>
       <c r="C91" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D91">
         <v>3</v>
       </c>
       <c r="E91" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K91" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="O91">
         <v>1</v>
@@ -5306,13 +5564,13 @@
         <v>0.05</v>
       </c>
       <c r="Q91" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R91" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S91" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U91">
         <v>1</v>
@@ -5320,22 +5578,22 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B92">
         <v>260421</v>
       </c>
       <c r="C92" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D92">
         <v>3</v>
       </c>
       <c r="E92" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K92" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="O92">
         <v>1</v>
@@ -5344,13 +5602,13 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="Q92" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R92" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S92" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U92">
         <v>1</v>
@@ -5358,22 +5616,22 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B93">
         <v>260421</v>
       </c>
       <c r="C93" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D93">
         <v>3</v>
       </c>
       <c r="E93" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K93" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="O93">
         <v>1</v>
@@ -5382,13 +5640,13 @@
         <v>0.1</v>
       </c>
       <c r="Q93" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R93" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S93" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U93">
         <v>1</v>
@@ -5396,22 +5654,22 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B94">
         <v>260421</v>
       </c>
       <c r="C94" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D94">
         <v>3</v>
       </c>
       <c r="E94" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K94" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O94">
         <v>1</v>
@@ -5420,13 +5678,13 @@
         <v>0.3</v>
       </c>
       <c r="Q94" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R94" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S94" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U94">
         <v>1</v>
@@ -5434,22 +5692,22 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B95">
         <v>260421</v>
       </c>
       <c r="C95" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D95">
         <v>3</v>
       </c>
       <c r="E95" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K95" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="O95">
         <v>1</v>
@@ -5458,13 +5716,13 @@
         <v>0.5</v>
       </c>
       <c r="Q95" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R95" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S95" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U95">
         <v>1</v>
@@ -5472,22 +5730,22 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B96">
         <v>260421</v>
       </c>
       <c r="C96" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D96">
         <v>3</v>
       </c>
       <c r="E96" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K96" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="O96">
         <v>1</v>
@@ -5496,13 +5754,13 @@
         <v>0.7</v>
       </c>
       <c r="Q96" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R96" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S96" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U96">
         <v>1</v>
@@ -5510,22 +5768,22 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B97">
         <v>260421</v>
       </c>
       <c r="C97" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D97">
         <v>3</v>
       </c>
       <c r="E97" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K97" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="O97">
         <v>1</v>
@@ -5534,13 +5792,13 @@
         <v>1</v>
       </c>
       <c r="Q97" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R97" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S97" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U97">
         <v>1</v>
@@ -5548,22 +5806,22 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B98">
         <v>260421</v>
       </c>
       <c r="C98" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D98">
         <v>3</v>
       </c>
       <c r="E98" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K98" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O98">
         <v>1</v>
@@ -5572,13 +5830,13 @@
         <v>1.5</v>
       </c>
       <c r="Q98" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R98" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S98" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U98">
         <v>1</v>
@@ -5586,22 +5844,22 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B99">
         <v>260421</v>
       </c>
       <c r="C99" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D99">
         <v>3</v>
       </c>
       <c r="E99" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K99" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O99">
         <v>1</v>
@@ -5610,13 +5868,13 @@
         <v>2</v>
       </c>
       <c r="Q99" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R99" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S99" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U99">
         <v>1</v>
@@ -5631,35 +5889,239 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{339D283A-FE1A-45B7-92D1-235ED49D7C2F}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.75" customWidth="1"/>
+    <col min="2" max="2" width="19.125" customWidth="1"/>
+    <col min="3" max="3" width="7.25" customWidth="1"/>
+    <col min="4" max="4" width="5.75" customWidth="1"/>
+    <col min="5" max="5" width="6.25" customWidth="1"/>
+    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="7" max="7" width="9.375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>153</v>
+        <v>26</v>
+      </c>
+      <c r="B1">
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" t="s">
         <v>154</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D3" t="s">
         <v>155</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E3" t="s">
         <v>156</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F3" t="s">
         <v>157</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G3" t="s">
         <v>158</v>
       </c>
-      <c r="F2" t="s">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>159</v>
       </c>
-      <c r="G2" t="s">
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E4">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>160</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D5">
+        <v>1.08</v>
+      </c>
+      <c r="E5">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D6">
+        <v>1.06</v>
+      </c>
+      <c r="E6">
+        <v>0.94000000000000006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D7">
+        <v>1.04</v>
+      </c>
+      <c r="E7">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8">
+        <v>1.02</v>
+      </c>
+      <c r="E8">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D10">
+        <v>0.98</v>
+      </c>
+      <c r="E10">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11">
+        <v>0.96</v>
+      </c>
+      <c r="E11">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12">
+        <v>0.94000000000000006</v>
+      </c>
+      <c r="E12">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13">
+        <v>0.92</v>
+      </c>
+      <c r="E13">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>169</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>170</v>
+      </c>
+      <c r="D14">
+        <v>0.9</v>
+      </c>
+      <c r="E14">
+        <v>1.1000000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/script/simulation_queue.xlsx
+++ b/script/simulation_queue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f03addda2663411/SRBL/WearableOptimizedControl/Optimizer/Moco_git/script/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="534" documentId="8_{985CFB64-8444-49E3-9649-B21738068EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECD64A8A-0EB7-4415-9074-DE620007DE88}"/>
+  <xr:revisionPtr revIDLastSave="535" documentId="8_{985CFB64-8444-49E3-9649-B21738068EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8D59CEB-A227-42D1-81A2-E46EABBA11C3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2"/>
   </bookViews>
@@ -2114,7 +2114,7 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>260513</t>
+    <t>260514</t>
   </si>
   <si>
     <t>soleus_r force 25.00% + soleus_r fiber 100.00%</t>

--- a/script/simulation_queue.xlsx
+++ b/script/simulation_queue.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{13E9C6D3-F6CD-4322-8640-D12336757B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8145CB92-DDCD-4A86-9E0E-9EDABC4DEBF8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="simulation_queue" sheetId="1" r:id="rId1"/>

--- a/script/simulation_queue.xlsx
+++ b/script/simulation_queue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f03addda2663411/SRBL/WearableOptimizedControl/Optimizer/Moco_git/script/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{13E9C6D3-F6CD-4322-8640-D12336757B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8145CB92-DDCD-4A86-9E0E-9EDABC4DEBF8}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{13E9C6D3-F6CD-4322-8640-D12336757B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F03DE8E6-6DBB-4E1D-8511-21CEABEE4184}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="simulation_queue" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7186" uniqueCount="1131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7228" uniqueCount="1137">
   <si>
     <t>SF</t>
   </si>
@@ -3554,6 +3554,30 @@
   </si>
   <si>
     <t>soleus_r,gastroc_r,tib_ant_r,rect_fem_r,hamstrings_r,bifemsh_r,glut_max_r,iliopsoas_r,vasti_r</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>debug_AF302-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>debug_AF339-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>debug_AF381-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>debug_AF409-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>debug_AF415-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>debug_AF432-3</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -4518,7 +4542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.75" customWidth="1"/>
@@ -4930,6 +4954,234 @@
       </c>
       <c r="U18">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B19">
+        <v>260515</v>
+      </c>
+      <c r="C19" t="s">
+        <v>708</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19" t="s">
+        <v>33</v>
+      </c>
+      <c r="K19" t="s">
+        <v>1131</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>485</v>
+      </c>
+      <c r="R19" t="s">
+        <v>486</v>
+      </c>
+      <c r="S19" t="s">
+        <v>633</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B20">
+        <v>260515</v>
+      </c>
+      <c r="C20" t="s">
+        <v>710</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20" t="s">
+        <v>33</v>
+      </c>
+      <c r="K20" t="s">
+        <v>1132</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>0.70099999999999996</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>485</v>
+      </c>
+      <c r="R20" t="s">
+        <v>486</v>
+      </c>
+      <c r="S20" t="s">
+        <v>633</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B21">
+        <v>260515</v>
+      </c>
+      <c r="C21" t="s">
+        <v>713</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21" t="s">
+        <v>33</v>
+      </c>
+      <c r="K21" t="s">
+        <v>1133</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>485</v>
+      </c>
+      <c r="R21" t="s">
+        <v>486</v>
+      </c>
+      <c r="S21" t="s">
+        <v>633</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B22">
+        <v>260515</v>
+      </c>
+      <c r="C22" t="s">
+        <v>715</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22" t="s">
+        <v>33</v>
+      </c>
+      <c r="K22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>485</v>
+      </c>
+      <c r="R22" t="s">
+        <v>486</v>
+      </c>
+      <c r="S22" t="s">
+        <v>633</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B23">
+        <v>260515</v>
+      </c>
+      <c r="C23" t="s">
+        <v>715</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23" t="s">
+        <v>33</v>
+      </c>
+      <c r="K23" t="s">
+        <v>1135</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>1.0049999999999999</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>485</v>
+      </c>
+      <c r="R23" t="s">
+        <v>486</v>
+      </c>
+      <c r="S23" t="s">
+        <v>633</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B24">
+        <v>260515</v>
+      </c>
+      <c r="C24" t="s">
+        <v>716</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24" t="s">
+        <v>33</v>
+      </c>
+      <c r="K24" t="s">
+        <v>1136</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <v>2.0049999999999999</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>485</v>
+      </c>
+      <c r="R24" t="s">
+        <v>486</v>
+      </c>
+      <c r="S24" t="s">
+        <v>633</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/script/simulation_queue.xlsx
+++ b/script/simulation_queue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f03addda2663411/SRBL/WearableOptimizedControl/Optimizer/Moco_git/script/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="13_ncr:1_{13E9C6D3-F6CD-4322-8640-D12336757B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{479E9B67-2427-4820-87A2-157717248B1D}"/>
+  <xr:revisionPtr revIDLastSave="216" documentId="13_ncr:1_{13E9C6D3-F6CD-4322-8640-D12336757B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C6AB0D5-1C12-4B26-ABA3-B80933D67775}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4585,92 +4585,112 @@
     <t>2D_gait_AFO_pc_60kg.osim</t>
   </si>
   <si>
-    <t>2D_gait_AFO_pc_60kg_v1.osim</t>
-  </si>
-  <si>
-    <t>2D_gait_AFO_pc_60kg_v2.osim</t>
-  </si>
-  <si>
-    <t>2D_gait_AFO_pc_60kg_v3.osim</t>
-  </si>
-  <si>
-    <t>2D_gait_AFO_pc_60kg_v4.osim</t>
-  </si>
-  <si>
-    <t>2D_gait_AFO_pc_60kg_v5.osim</t>
-  </si>
-  <si>
     <t>2D_gait_AFO_pc_70kg.osim</t>
   </si>
   <si>
-    <t>2D_gait_AFO_pc_70kg_v1.osim</t>
-  </si>
-  <si>
-    <t>2D_gait_AFO_pc_70kg_v2.osim</t>
-  </si>
-  <si>
-    <t>2D_gait_AFO_pc_70kg_v3.osim</t>
-  </si>
-  <si>
-    <t>2D_gait_AFO_pc_70kg_v4.osim</t>
-  </si>
-  <si>
-    <t>2D_gait_AFO_pc_70kg_v5.osim</t>
-  </si>
-  <si>
     <t>2D_gait_AFO_pc_80kg.osim</t>
   </si>
   <si>
-    <t>2D_gait_AFO_pc_80kg_v1.osim</t>
-  </si>
-  <si>
-    <t>2D_gait_AFO_pc_80kg_v2.osim</t>
-  </si>
-  <si>
-    <t>2D_gait_AFO_pc_80kg_v3.osim</t>
-  </si>
-  <si>
-    <t>2D_gait_AFO_pc_80kg_v4.osim</t>
-  </si>
-  <si>
-    <t>2D_gait_AFO_pc_80kg_v5.osim</t>
-  </si>
-  <si>
     <t>2D_gait_AFO_pc_90kg.osim</t>
   </si>
   <si>
-    <t>2D_gait_AFO_pc_90kg_v1.osim</t>
-  </si>
-  <si>
-    <t>2D_gait_AFO_pc_90kg_v2.osim</t>
-  </si>
-  <si>
-    <t>2D_gait_AFO_pc_90kg_v3.osim</t>
-  </si>
-  <si>
-    <t>2D_gait_AFO_pc_90kg_v4.osim</t>
-  </si>
-  <si>
-    <t>2D_gait_AFO_pc_90kg_v5.osim</t>
-  </si>
-  <si>
-    <t>2D_gait_AFO_pc_50kg_v1.osim</t>
+    <t>2D_gait_AFO_pc_50kg_150cm_R1.osim</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>2D_gait_AFO_pc_50kg_v2.osim</t>
+    <t>2D_gait_AFO_pc_50kg_160cm_R1.osim</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>2D_gait_AFO_pc_50kg_v3.osim</t>
+    <t>2D_gait_AFO_pc_50kg_170cm_R1.osim</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>2D_gait_AFO_pc_50kg_v5.osim</t>
+    <t>2D_gait_AFO_pc_50kg_180cm_R1.osim</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>2D_gait_AFO_pc_50kg_v4.osim</t>
+    <t>2D_gait_AFO_pc_50kg_190cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_60kg_150cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_60kg_160cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_60kg_170cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_60kg_180cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_60kg_190cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_70kg_150cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_70kg_160cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_70kg_170cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_70kg_180cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_70kg_190cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_80kg_150cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_80kg_160cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_80kg_170cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_80kg_180cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_80kg_190cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_90kg_150cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_90kg_160cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_90kg_170cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_90kg_180cm_R1.osim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D_gait_AFO_pc_90kg_190cm_R1.osim</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -65088,7 +65108,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="B4">
         <v>5</v>
@@ -65096,7 +65116,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1481</v>
+        <v>1471</v>
       </c>
       <c r="B5">
         <v>5</v>
@@ -65104,7 +65124,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1487</v>
+        <v>1472</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -65873,7 +65893,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1493</v>
+        <v>1473</v>
       </c>
       <c r="B47" t="s">
         <v>1467</v>
@@ -65890,7 +65910,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1494</v>
+        <v>1474</v>
       </c>
       <c r="B48" t="s">
         <v>1467</v>
@@ -65907,7 +65927,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1495</v>
+        <v>1475</v>
       </c>
       <c r="B49" t="s">
         <v>1467</v>
@@ -65924,7 +65944,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1497</v>
+        <v>1476</v>
       </c>
       <c r="B50" t="s">
         <v>1467</v>
@@ -65941,7 +65961,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1496</v>
+        <v>1477</v>
       </c>
       <c r="B51" t="s">
         <v>1467</v>
@@ -65958,7 +65978,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1470</v>
+        <v>1478</v>
       </c>
       <c r="B52" t="s">
         <v>1469</v>
@@ -65975,7 +65995,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1471</v>
+        <v>1479</v>
       </c>
       <c r="B53" t="s">
         <v>1469</v>
@@ -65992,7 +66012,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1472</v>
+        <v>1480</v>
       </c>
       <c r="B54" t="s">
         <v>1469</v>
@@ -66009,7 +66029,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1473</v>
+        <v>1481</v>
       </c>
       <c r="B55" t="s">
         <v>1469</v>
@@ -66026,7 +66046,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1474</v>
+        <v>1482</v>
       </c>
       <c r="B56" t="s">
         <v>1469</v>
@@ -66043,10 +66063,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1476</v>
+        <v>1483</v>
       </c>
       <c r="B57" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="C57" t="s">
         <v>1468</v>
@@ -66060,10 +66080,10 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1477</v>
+        <v>1484</v>
       </c>
       <c r="B58" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="C58" t="s">
         <v>1468</v>
@@ -66077,10 +66097,10 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1478</v>
+        <v>1485</v>
       </c>
       <c r="B59" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="C59" t="s">
         <v>1468</v>
@@ -66094,10 +66114,10 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="B60" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="C60" t="s">
         <v>1468</v>
@@ -66111,10 +66131,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1480</v>
+        <v>1487</v>
       </c>
       <c r="B61" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="C61" t="s">
         <v>1468</v>
@@ -66128,10 +66148,10 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1482</v>
+        <v>1488</v>
       </c>
       <c r="B62" t="s">
-        <v>1481</v>
+        <v>1471</v>
       </c>
       <c r="C62" t="s">
         <v>1468</v>
@@ -66145,10 +66165,10 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1483</v>
+        <v>1489</v>
       </c>
       <c r="B63" t="s">
-        <v>1481</v>
+        <v>1471</v>
       </c>
       <c r="C63" t="s">
         <v>1468</v>
@@ -66162,10 +66182,10 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1484</v>
+        <v>1490</v>
       </c>
       <c r="B64" t="s">
-        <v>1481</v>
+        <v>1471</v>
       </c>
       <c r="C64" t="s">
         <v>1468</v>
@@ -66179,10 +66199,10 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1485</v>
+        <v>1491</v>
       </c>
       <c r="B65" t="s">
-        <v>1481</v>
+        <v>1471</v>
       </c>
       <c r="C65" t="s">
         <v>1468</v>
@@ -66196,10 +66216,10 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="B66" t="s">
-        <v>1481</v>
+        <v>1471</v>
       </c>
       <c r="C66" t="s">
         <v>1468</v>
@@ -66213,10 +66233,10 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1488</v>
+        <v>1493</v>
       </c>
       <c r="B67" t="s">
-        <v>1487</v>
+        <v>1472</v>
       </c>
       <c r="C67" t="s">
         <v>1468</v>
@@ -66230,10 +66250,10 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1489</v>
+        <v>1494</v>
       </c>
       <c r="B68" t="s">
-        <v>1487</v>
+        <v>1472</v>
       </c>
       <c r="C68" t="s">
         <v>1468</v>
@@ -66247,10 +66267,10 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1490</v>
+        <v>1495</v>
       </c>
       <c r="B69" t="s">
-        <v>1487</v>
+        <v>1472</v>
       </c>
       <c r="C69" t="s">
         <v>1468</v>
@@ -66264,10 +66284,10 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1491</v>
+        <v>1496</v>
       </c>
       <c r="B70" t="s">
-        <v>1487</v>
+        <v>1472</v>
       </c>
       <c r="C70" t="s">
         <v>1468</v>
@@ -66281,10 +66301,10 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1492</v>
+        <v>1497</v>
       </c>
       <c r="B71" t="s">
-        <v>1487</v>
+        <v>1472</v>
       </c>
       <c r="C71" t="s">
         <v>1468</v>
